--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -903,7 +903,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>4.05pm</t>
+          <t>4.36pm</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>7.50pm · Dinner near Indian Music Experience Museum</t>
+          <t>7.40pm · Dinner near Indian Music Experience Museum</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>9.08am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -1263,12 +1263,12 @@
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>10.20pm · Dinner near Sabha Bengaluru (late return)</t>
+          <t>10.10pm · Dinner near Sabha Bengaluru (late return)</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Late night: lights out at 1.16am (+1).</t>
+          <t>2 of 25 artists travel today; 23 stay at the stay. · Late night: lights out at 1.07am (+1).</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1371,12 +1371,12 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>4.05pm</t>
+          <t>4.36pm</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.50pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1386,139 +1386,85 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 05 · 37 km · typical traffic for the day · 10 min loading first</t>
+          <t>1 h 04 · 37 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.50pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>6.00pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>5.30pm</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>5.40pm</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Sound check</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr"/>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>6.00pm</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>7.30pm</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>LECTURE DEMONSTRATION</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Talk · Indian Music Experience Museum, JP Nagar 7th Phase · 2 artists</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>7.40pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr"/>
     </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>6.00pm</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>LECTURE DEMONSTRATION</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Talk · Indian Music Experience Museum, JP Nagar 7th Phase · 25 artists</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>7.35pm</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>7.35pm</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>7.50pm</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>7.50pm</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>8.50pm</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>7.40pm</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>8.40pm</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>Dinner near Indian Music Experience Museum</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>added: the plan has dinner back at the stay</t>
         </is>
@@ -4736,7 +4682,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4791,12 +4737,12 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>9.08am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>10.17am</t>
+          <t>10.48am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -4806,24 +4752,24 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>59 min · 33 km · typical traffic for the day · 10 min loading first</t>
+          <t>1 h 03 · 24 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>10.17am</t>
+          <t>10.48am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>10.27am</t>
+          <t>10.58am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr"/>
@@ -4831,154 +4777,100 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>10.27am</t>
+          <t>10.58am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>10.37am</t>
+          <t>11.00am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Spare time at the venue</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>10.37am</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>10.57am</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr"/>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>11.00am</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>10.00pm</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>CLOSING DAY</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Talk · Sabha Bengaluru, Shivajinagar · 2 artists</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>10.57am</t>
+          <t>12.00pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>11.00am</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>11.00am</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="C10" s="15" t="inlineStr">
+        <is>
+          <t>Lunch at the venue (packed)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>During “Closing Day” — arrange packed lunch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>10.00pm</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>CLOSING DAY</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Talk · Sabha Bengaluru, Shivajinagar · 25 artists</t>
-        </is>
-      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>10.10pm</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>12.00pm</t>
+          <t>10.10pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>1.00pm</t>
+          <t>11.10pm</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Lunch at the venue (packed)</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>During “Closing Day” — arrange packed lunch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>10.00pm</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>10.05pm</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>10.05pm</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>10.20pm</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>10.20pm</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>11.20pm</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
-        <is>
           <t>Dinner near Sabha Bengaluru (late return)</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr"/>
+      <c r="D12" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -839,12 +839,12 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>10.20pm · Dinner near PCPA (Prestige Centre for Performing Arts) (late return)</t>
+          <t>9.20pm · Dinner near PCPA (Prestige Centre for Performing Arts)</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Late night: lights out at 1.06am (+1).</t>
+          <t>Dinner added before leaving the venue; the plan itself has dinner at the stay after the drive back.</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>10.20pm · Dinner near PCPA (Prestige Centre for Performing Arts) (late return)</t>
+          <t>9.20pm · Dinner near PCPA (Prestige Centre for Performing Arts)</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>Short night: 5 h 54 between lights out (1.06am (+1)) and wake-up. · Late night: lights out at 1.06am (+1).</t>
+          <t>Dinner added before leaving the venue; the plan itself has dinner at the stay after the drive back.</t>
         </is>
       </c>
     </row>
@@ -6088,7 +6088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6118,82 +6118,71 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>• Dinner added before leaving the venue; the plan itself has dinner at the stay after the drive back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Where / detail</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>4.23pm</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>5.25pm</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>→ Leave the stay for PCPA (Prestige Centre for Performing Arts)</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>52 min · 30 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>5.25pm</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>5.35pm</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
+          <t>5.25pm</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
           <t>5.35pm</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>5.45pm</t>
-        </is>
-      </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
@@ -6201,75 +6190,75 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
+          <t>5.35pm</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
           <t>5.45pm</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>5.45pm</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>10.00pm</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>KECAK WORKSHOP</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>Workshop · PCPA (Prestige Centre for Performing Arts), Konanakunte, Kanakapura Road · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>10.00pm</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>10.05pm</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>10.05pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>10.20pm</t>
+          <t>9.05pm</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr"/>
@@ -6277,22 +6266,47 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
+          <t>9.05pm</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
           <t>10.20pm</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>11.20pm</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>Dinner near PCPA (Prestige Centre for Performing Arts) (late return)</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr"/>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Dinner near PCPA (Prestige Centre for Performing Arts)</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>added: the plan has dinner back at the stay</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:D4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6304,7 +6318,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6334,82 +6348,71 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>• Dinner added before leaving the venue; the plan itself has dinner at the stay after the drive back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Where / detail</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>4.21pm</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>5.25pm</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>→ Leave the stay for PCPA (Prestige Centre for Performing Arts)</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>54 min · 30 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>5.25pm</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>5.35pm</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
+          <t>5.25pm</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
           <t>5.35pm</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>5.45pm</t>
-        </is>
-      </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
@@ -6417,75 +6420,75 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
+          <t>5.35pm</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
           <t>5.45pm</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>5.45pm</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>10.00pm</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>KECAK WORKSHOP</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>Workshop · PCPA (Prestige Centre for Performing Arts), Konanakunte, Kanakapura Road · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>10.00pm</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>10.05pm</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>10.05pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>10.20pm</t>
+          <t>9.05pm</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr"/>
@@ -6493,22 +6496,47 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
+          <t>9.05pm</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
           <t>10.20pm</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>11.20pm</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>Dinner near PCPA (Prestige Centre for Performing Arts) (late return)</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr"/>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Dinner near PCPA (Prestige Centre for Performing Arts)</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>added: the plan has dinner back at the stay</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:D4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -935,7 +935,7 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Workshop for Students 10.00am; Traditional Balinese Dance 7.00pm</t>
+          <t>Workshop for Students 10.00am; Traditional Balinese Dance 5.00pm</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>9.20pm · Dinner near Meenakshi Rangamancha</t>
+          <t>7.20pm · Dinner near Meenakshi Rangamancha</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
@@ -1511,7 +1511,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Workshop for Students 10.00am · Traditional Balinese Dance 7.00pm</t>
+          <t>Workshop for Students 10.00am · Traditional Balinese Dance 5.00pm</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>4.45pm</t>
+          <t>2.46pm</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -1717,12 +1717,12 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>4.45pm</t>
+          <t>2.46pm</t>
         </is>
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>3.00pm</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
@@ -1732,19 +1732,19 @@
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>15 min · 5 km · typical traffic for the day</t>
+          <t>14 min · 5 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>3.00pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1757,12 +1757,12 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>4.00pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -1775,12 +1775,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>4.00pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>7.00pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1793,12 +1793,12 @@
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>7.00pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>8.30pm</t>
+          <t>6.30pm</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
@@ -1815,12 +1815,12 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>8.30pm</t>
+          <t>6.30pm</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>8.50pm</t>
+          <t>6.50pm</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -1833,12 +1833,12 @@
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>8.50pm</t>
+          <t>6.50pm</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -1851,12 +1851,12 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>10.20pm</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -729,12 +729,12 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>An Evening of Kecak - Inaugural Public Performance 6.00pm</t>
+          <t>An Evening of Kecak - Inaugural Public Performance 5.30pm</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>2.28pm</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>8.20pm · Dinner near Orion Mall</t>
+          <t>7.50pm · Dinner near Orion Mall</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Dance Movement Workshop 9.00am; Indonesian Shadow Puppetry Performance 3.30pm</t>
+          <t>Dance Movement Workshop 9.00am; Shadow Puppetry Performance 3.30pm</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>“Indonesian Shadow Puppetry Performance”: arrives 1.51pm, 21 min late for the 120 min preparation. · Late night: lights out at 1.16am (+1).</t>
+          <t>“Shadow Puppetry Performance”: arrives 1.51pm, 21 min late for the 120 min preparation. · Late night: lights out at 1.16am (+1).</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>Balinese Shadow Puppetry Workshop 10.00am; Kecak Performance 7.00pm</t>
+          <t>Shadow Puppetry Workshop 10.00am; Kecak Performance 5.30pm</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>9.20pm · Dinner near PCPA (Prestige Centre for Performing Arts)</t>
+          <t>7.50pm · Dinner near PCPA (Prestige Centre for Performing Arts)</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>Balinese Shadow Puppetry Workshop 10.00am; Indonesian × Indian Shadow Puppetry Performance 7.30pm</t>
+          <t>Shadow Puppetry Workshop 10.00am; Indonesian × Indian Puppetry Act 6.30pm</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -1045,10 +1045,14 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>9.50pm · Dinner near Mandala Cultural Centre (late return)</t>
-        </is>
-      </c>
-      <c r="G18" s="6" t="inlineStr"/>
+          <t>8.50pm · Dinner near Mandala Cultural Centre</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Dinner added before leaving the venue; the plan itself has dinner at the stay after the drive back.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1063,12 +1067,12 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Traditional Balinese Dance × Yakshagana Performance 7.00pm</t>
+          <t>Traditional Balinese Dance × Yakshagana Performance 6.00pm</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>3.58pm</t>
+          <t>3.00pm</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -1078,12 +1082,12 @@
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>9.50pm · Dinner near Chowdiah Memorial Hall (late return)</t>
+          <t>8.20pm · Dinner near Chowdiah Memorial Hall</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>6 Yakshagana artists (local) perform with the group today and travel on their own.</t>
+          <t>Dinner added before leaving the venue; the plan itself has dinner at the stay after the drive back.</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1104,7 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>Mask Making Workshop 10.00am; Gamelan workshop 6.00pm</t>
+          <t>Mask Making Workshop 10.00am; Gamelan workshop 5.00pm</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1992,7 +1996,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Balinese Shadow Puppetry Workshop 10.00am · Kecak Performance 7.00pm</t>
+          <t>Shadow Puppetry Workshop 10.00am · Kecak Performance 5.30pm</t>
         </is>
       </c>
     </row>
@@ -2132,12 +2136,12 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>BALINESE SHADOW PUPPETRY WORKSHOP</t>
+          <t>SHADOW PUPPETRY WORKSHOP</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>Workshop · Mandala Cultural Centre, Talaghattapura, Kanakapura Road · 25 artists</t>
+          <t>Workshop · Mandala Cultural Centre, Talaghattapura, Kanakapura Road</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2189,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>4.28pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -2216,12 +2220,12 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>4.28pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>4.46pm</t>
+          <t>3.14pm</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -2231,19 +2235,19 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>18 min · 5 km · typical traffic for the day</t>
+          <t>17 min · 5 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>4.46pm</t>
+          <t>3.14pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>3.59pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -2256,12 +2260,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>3.59pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>6.01pm</t>
+          <t>4.29pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -2274,12 +2278,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>6.01pm</t>
+          <t>4.29pm</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>7.00pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -2292,12 +2296,12 @@
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
+          <t>5.30pm</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
           <t>7.00pm</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
-        <is>
-          <t>8.30pm</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
@@ -2314,12 +2318,12 @@
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>8.30pm</t>
+          <t>7.00pm</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>8.50pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -2332,12 +2336,12 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>8.50pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>7.50pm</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -2350,12 +2354,12 @@
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>7.50pm</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>10.20pm</t>
+          <t>8.50pm</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
@@ -2378,676 +2382,6 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="008C8E92"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="64" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>BALI IN BENGALURU · DAILY ROUTINE</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 12 Oct</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Balinese Shadow Puppetry Workshop 10.00am · Indonesian × Indian Shadow Puppetry Performance 7.30pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>From</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>To</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>What</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Where / detail</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>8.30am</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>9.14am</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>→ Leave the stay for Mandala Cultural Centre</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>34 min · 25 km · typical traffic for the day · 10 min loading first</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>9.14am</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>9.24am</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>9.24am</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>9.34am</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Sound check</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>9.34am</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>9.49am</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>9.49am</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>10.00am</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>10.00am</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>BALINESE SHADOW PUPPETRY WORKSHOP</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Workshop · Mandala Cultural Centre, Talaghattapura, Kanakapura Road · 25 artists</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>1.05pm</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>1.05pm</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>1.20pm</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>1.20pm</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>1.52pm</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>→ Back to the stay</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>32 min · 25 km · typical traffic for the day</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>1.52pm</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>4.47pm</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>At the stay — rest</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>1.52pm</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>2.52pm</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>Lunch at the stay</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>4.35pm</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>5.21pm</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>→ Leave the stay for Mandala Cultural Centre</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>36 min · 25 km · typical traffic for the day · 10 min loading first</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>5.21pm</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>5.51pm</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>5.51pm</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
-        <is>
-          <t>6.21pm</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Sound check</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>6.21pm</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t>7.21pm</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>7.21pm</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>INDONESIAN × INDIAN SHADOW PUPPETRY PERFORMANCE</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>Performance · Mandala Cultural Centre, Talaghattapura, Kanakapura Road · 25 artists</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C25" s="15" t="inlineStr">
-        <is>
-          <t>Dinner near Mandala Cultural Centre (late return)</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="008C8E92"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="52" customWidth="1" min="3" max="3"/>
-    <col width="64" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>BALI IN BENGALURU · DAILY ROUTINE</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 13 Oct</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Traditional Balinese Dance × Yakshagana Performance 7.00pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="16" t="inlineStr">
-        <is>
-          <t>• 6 Yakshagana artists (local) perform with the group today and travel on their own.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>From</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>To</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>What</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>Where / detail</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
-        <is>
-          <t>3.58pm</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>→ Leave the stay for Chowdiah Memorial Hall</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>52 min · 27 km · typical traffic for the day · 10 min loading first</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>5.30pm</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>5.30pm</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>6.00pm</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Sound check</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>6.00pm</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>7.00pm</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>7.00pm</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>TRADITIONAL BALINESE DANCE × YAKSHAGANA PERFORMANCE</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>Performance · Chowdiah Memorial Hall, Vyalikaval, Malleshwaram · 25 artists</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
-        <is>
-          <t>Dinner near Chowdiah Memorial Hall (late return)</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A4:D4"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="008C8E92"/>
@@ -3073,14 +2407,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Wed, 14 Oct</t>
+          <t>Mon, 12 Oct</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Mask Making Workshop 10.00am · Gamelan workshop 6.00pm</t>
+          <t>Shadow Puppetry Workshop 10.00am · Indonesian × Indian Puppetry Act 6.30pm</t>
         </is>
       </c>
     </row>
@@ -3116,34 +2450,34 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>8.15am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>→ Leave the stay for PARSEC, Jayanagar (Maker's Adda)</t>
+          <t>→ Leave the stay for Mandala Cultural Centre</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>59 min · 35 km · typical traffic for the day · 10 min loading first</t>
+          <t>34 min · 25 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
+          <t>9.14am</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
           <t>9.24am</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>9.34am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3156,12 +2490,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
+          <t>9.24am</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
           <t>9.34am</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>9.44am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3174,6 +2508,662 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
+          <t>9.34am</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>9.49am</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>9.49am</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>10.00am</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>10.00am</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY WORKSHOP</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Workshop · Mandala Cultural Centre, Talaghattapura, Kanakapura Road</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>1.05pm</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>1.05pm</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>1.20pm</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>1.20pm</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>4.30pm</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Hold at Mandala Cultural Centre</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>1.20pm</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>2.20pm</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
+        <is>
+          <t>Lunch near Mandala Cultural Centre</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>4.30pm</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>4.30pm</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>→ Leave Mandala Cultural Centre for Mandala Cultural Centre</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>0 min · 0 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>4.30pm</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>5.30pm</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>5.30pm</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>6.30pm</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>6.30pm</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>8.00pm</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>INDONESIAN × INDIAN PUPPETRY ACT</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Performance · Mandala Cultural Centre, Talaghattapura, Kanakapura Road</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>8.00pm</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>8.20pm</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>8.20pm</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>8.50pm</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>8.50pm</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Dinner near Mandala Cultural Centre</t>
+        </is>
+      </c>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>added: the plan has dinner back at the stay</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:D4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="008C8E92"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="64" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BALI IN BENGALURU · DAILY ROUTINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Traditional Balinese Dance × Yakshagana Performance 6.00pm</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>• 6 Yakshagana artists (local) perform with the group today and travel on their own.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>• Dinner added before leaving the venue; the plan itself has dinner at the stay after the drive back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Where / detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>3.00pm</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>4.00pm</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>→ Leave the stay for Chowdiah Memorial Hall</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>50 min · 27 km · typical traffic for the day · 10 min loading first</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>4.00pm</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>4.30pm</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>4.30pm</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>6.00pm</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>6.00pm</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>7.30pm</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>TRADITIONAL BALINESE DANCE × YAKSHAGANA PERFORMANCE</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Performance · Chowdiah Memorial Hall, Vyalikaval, Malleshwaram · 25 artists</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>7.30pm</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>7.50pm</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>7.50pm</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>8.20pm</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>8.20pm</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Dinner near Chowdiah Memorial Hall</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>added: the plan has dinner back at the stay</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A4:D4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="008C8E92"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="64" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BALI IN BENGALURU · DAILY ROUTINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 14 Oct</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Mask Making Workshop 10.00am · Gamelan workshop 5.00pm</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>• Dinner added before leaving the venue; the plan itself has dinner at the stay after the drive back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>What</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Where / detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>8.15am</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>9.24am</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>→ Leave the stay for PARSEC, Jayanagar (Maker's Adda)</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>59 min · 35 km · typical traffic for the day · 10 min loading first</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>9.24am</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>9.34am</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>9.34am</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>9.44am</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
           <t>9.44am</t>
         </is>
       </c>
@@ -3248,99 +3238,95 @@
       <c r="D13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="14" t="inlineStr">
         <is>
           <t>1.20pm</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>2.18pm</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>→ Back to the stay</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>58 min · 24 km · typical traffic for the day</t>
-        </is>
-      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>4.16pm</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Hold in town near PARSEC, Jayanagar (Maker's Adda)</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>2.18pm</t>
+          <t>1.20pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>4.08pm</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>At the stay — rest</t>
+          <t>2.20pm</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Lunch near PARSEC, Jayanagar (Maker's Adda)</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>2.18pm</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>3.18pm</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>Lunch at the stay</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr"/>
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>4.16pm</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>4.25pm</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>→ Leave PARSEC, Jayanagar (Maker's Adda) for Jama The Studio</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>9 min · 2 km · typical traffic for the day</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>4.08pm</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>5.25pm</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>→ Leave the stay for Jama The Studio</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>1 h 07 · 36 km · typical traffic for the day · 10 min loading first</t>
-        </is>
-      </c>
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>4.25pm</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>4.35pm</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>5.25pm</t>
+          <t>4.35pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>5.35pm</t>
+          <t>4.45pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr"/>
@@ -3348,75 +3334,75 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>5.35pm</t>
+          <t>4.45pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>5.45pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>5.45pm</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t>6.00pm</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>6.00pm</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>8.00pm</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>GAMELAN WORKSHOP</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>Workshop · Jama The Studio, Jayanagar 2nd Block · 25 artists</t>
         </is>
       </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>8.00pm</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>8.05pm</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>8.00pm</t>
+          <t>8.05pm</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>8.05pm</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
@@ -3424,38 +3410,20 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>8.05pm</t>
+          <t>8.20pm</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>8.20pm</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>8.20pm</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="C24" s="15" t="inlineStr">
+      <c r="C23" s="15" t="inlineStr">
         <is>
           <t>Dinner near Jama The Studio</t>
         </is>
       </c>
-      <c r="D24" s="18" t="inlineStr">
+      <c r="D23" s="18" t="inlineStr">
         <is>
           <t>added: the plan has dinner back at the stay</t>
         </is>
@@ -5409,7 +5377,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>An Evening of Kecak - Inaugural Public Performance 6.00pm</t>
+          <t>An Evening of Kecak - Inaugural Public Performance 5.30pm</t>
         </is>
       </c>
     </row>
@@ -5445,12 +5413,12 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>2.28pm</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4.00pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5467,12 +5435,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
+          <t>3.30pm</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
           <t>4.00pm</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>4.30pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5485,12 +5453,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
+          <t>4.00pm</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
           <t>4.30pm</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5503,12 +5471,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5521,12 +5489,12 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>7.30pm</t>
+          <t>7.00pm</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -5543,12 +5511,12 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>7.30pm</t>
+          <t>7.00pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>7.50pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -5561,12 +5529,12 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
+          <t>7.20pm</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
           <t>7.50pm</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>8.20pm</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -5579,12 +5547,12 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>8.20pm</t>
+          <t>7.50pm</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>8.50pm</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
@@ -5639,7 +5607,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Dance Movement Workshop 9.00am · Indonesian Shadow Puppetry Performance 3.30pm</t>
+          <t>Dance Movement Workshop 9.00am · Shadow Puppetry Performance 3.30pm</t>
         </is>
       </c>
     </row>
@@ -5910,12 +5878,12 @@
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>INDONESIAN SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>Performance · Jagriti Theatre, Whitefield · 25 artists</t>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
     </row>
@@ -5932,12 +5900,12 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>INDONESIAN SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>Performance · Jagriti Theatre, Whitefield · 25 artists</t>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -940,7 +940,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>8.30am</t>
+          <t>8.29am</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>8.20pm · Dinner near Jama The Studio</t>
+          <t>7.50pm · Dinner near Jama The Studio</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>8.30am</t>
+          <t>8.29am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>45 min · 28 km · typical traffic for the day · 10 min loading first</t>
+          <t>46 min · 28 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3111,7 +3111,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -3121,19 +3121,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>59 min · 35 km · typical traffic for the day · 10 min loading first</t>
+          <t>58 min · 35 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3146,12 +3146,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.43am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3164,12 +3164,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.43am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.59am</t>
+          <t>9.58am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3179,60 +3179,60 @@
       </c>
       <c r="D10" s="7" t="inlineStr"/>
     </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>9.58am</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>10.00am</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>10.00am</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>1.00pm</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>MASK MAKING WORKSHOP</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>Workshop · PARSEC, Jayanagar (Maker's Adda), Jayanagar 7th Block · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>1.05pm</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
           <t>1.05pm</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>1.20pm</t>
-        </is>
-      </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr"/>
@@ -3240,17 +3240,17 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
+          <t>1.05pm</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
           <t>1.20pm</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>4.16pm</t>
-        </is>
-      </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Hold in town near PARSEC, Jayanagar (Maker's Adda)</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr"/>
@@ -3263,70 +3263,70 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
+          <t>4.16pm</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Hold in town near PARSEC, Jayanagar (Maker's Adda)</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>1.20pm</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
           <t>2.20pm</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>Lunch near PARSEC, Jayanagar (Maker's Adda)</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>4.16pm</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>4.25pm</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>→ Leave PARSEC, Jayanagar (Maker's Adda) for Jama The Studio</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>9 min · 2 km · typical traffic for the day</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>4.25pm</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>4.35pm</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
+          <t>4.25pm</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
           <t>4.35pm</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>4.45pm</t>
-        </is>
-      </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr"/>
@@ -3334,75 +3334,75 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
+          <t>4.35pm</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
           <t>4.45pm</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>4.45pm</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>5.00pm</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>5.00pm</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>8.00pm</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>7.30pm</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>GAMELAN WORKSHOP</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>Workshop · Jama The Studio, Jayanagar 2nd Block · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>8.00pm</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>8.05pm</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>8.05pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>8.20pm</t>
+          <t>7.35pm</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
@@ -3410,20 +3410,38 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>8.20pm</t>
+          <t>7.35pm</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C23" s="15" t="inlineStr">
+          <t>7.50pm</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>7.50pm</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>8.50pm</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>Dinner near Jama The Studio</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="D24" s="18" t="inlineStr">
         <is>
           <t>added: the plan has dinner back at the stay</t>
         </is>
@@ -3444,7 +3462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3504,7 +3522,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -3514,19 +3532,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>59 min · 35 km · typical traffic for the day · 10 min loading first</t>
+          <t>58 min · 35 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -3539,12 +3557,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.43am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3557,12 +3575,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.43am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.59am</t>
+          <t>9.58am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3572,103 +3590,103 @@
       </c>
       <c r="D9" s="7" t="inlineStr"/>
     </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>9.58am</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>10.00am</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>10.00am</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>1.00pm</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>MASK MAKING WORKSHOP</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>Workshop · PARSEC, Jayanagar (Maker's Adda), Jayanagar 7th Block · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>1.05pm</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
           <t>1.05pm</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>1.05pm</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>1.20pm</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>1.20pm</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>2.17pm</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>→ Back to the stay</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>57 min · 24 km · typical traffic for the day</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>2.17pm</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>4.12pm</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>At the stay — rest</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -3678,70 +3696,70 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
+          <t>4.12pm</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>At the stay — rest</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>2.17pm</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
           <t>3.17pm</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>Lunch at the stay</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>4.12pm</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>5.30pm</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>→ Leave the stay for Yuvapatha</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>1 h 08 · 37 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>5.30pm</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>6.00pm</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
+          <t>5.30pm</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>6.30pm</t>
-        </is>
-      </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr"/>
@@ -3749,75 +3767,75 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
+          <t>6.00pm</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
           <t>6.30pm</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>6.30pm</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>BALINESE SHADOW PUPPETRY PERFORMANCE</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>Performance · Yuvapatha, Jayanagar · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
@@ -3825,17 +3843,17 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C23" s="15" t="inlineStr">
-        <is>
-          <t>Dinner near Yuvapatha</t>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr"/>
@@ -3843,34 +3861,52 @@
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
           <t>10.50pm</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Dinner near Yuvapatha</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>11.45pm</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Wait for the coach at Yuvapatha</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>11.45pm</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr"/>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="B26" s="11" t="inlineStr"/>
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>→ Leave Yuvapatha for Manipal University — overnight drive</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
+      <c r="D26" s="13" t="inlineStr">
         <is>
           <t>7 h 32 · 413 km · typical traffic for the day · sleep on the road</t>
         </is>
@@ -4167,7 +4203,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>7 h 42 · 385 km · typical traffic for the day · home about 5.32am (+1)</t>
+          <t>7 h 48 · 378 km · typical traffic for the day · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4630,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 35 · 52 km · typical traffic for the day · 10 min loading first</t>
+          <t>1 h 35 · 52 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -1257,7 +1257,7 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4630,19 +4630,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 35 · 52 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>1 h 06 · 48 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>7.30pm</t>
+          <t>7.01pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -4741,7 +4741,7 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>1 h 03 · 24 km · typical traffic for the day · 10 min loading first</t>
+          <t>1 h 04 · 24 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5211,7 +5211,7 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>31 min · 25 km · typical traffic for the day · 10 min loading first</t>
+          <t>31 min · 25 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -4620,7 +4620,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4630,19 +4630,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 06 · 48 km · live traffic · 10 min loading first</t>
+          <t>1 h 04 · 48 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>7.01pm</t>
+          <t>6.59pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.21am</t>
+          <t>6.19am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5211,19 +5211,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>31 min · 25 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>29 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.21am</t>
+          <t>6.19am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.31am</t>
+          <t>6.29am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5236,12 +5236,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.31am</t>
+          <t>6.29am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.46am</t>
+          <t>6.44am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5254,7 +5254,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.46am</t>
+          <t>6.44am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>52 min · 24 km · typical traffic for the day · 10 min loading first</t>
+          <t>52 min · 24 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -4620,7 +4620,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4630,19 +4630,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 04 · 48 km · live traffic · 10 min loading first</t>
+          <t>1 h 03 · 50 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.59pm</t>
+          <t>6.58pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.19am</t>
+          <t>6.22am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5211,19 +5211,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>29 min · 25 km · live traffic · 10 min loading first</t>
+          <t>32 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.19am</t>
+          <t>6.22am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.29am</t>
+          <t>6.32am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5236,12 +5236,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.29am</t>
+          <t>6.32am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.44am</t>
+          <t>6.47am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5254,7 +5254,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.44am</t>
+          <t>6.47am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>44 min · 28 km · typical traffic for the day · 10 min loading first</t>
+          <t>44 min · 28 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>1 h 01 · 26 km · typical traffic for the day</t>
+          <t>1 h 01 · 26 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.35pm</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4630,19 +4630,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 03 · 50 km · live traffic · 10 min loading first</t>
+          <t>1 h 04 · 48 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.58pm</t>
+          <t>6.59pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5201,7 +5201,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.22am</t>
+          <t>6.21am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5211,19 +5211,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>32 min · 25 km · live traffic · 10 min loading first</t>
+          <t>31 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.22am</t>
+          <t>6.21am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.32am</t>
+          <t>6.31am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5236,12 +5236,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.32am</t>
+          <t>6.31am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.47am</t>
+          <t>6.46am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5254,7 +5254,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.47am</t>
+          <t>6.46am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5387,7 +5387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5449,12 +5449,12 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.35pm</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>3.13pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5464,19 +5464,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>52 min · 24 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>28 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>3.13pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>4.00pm</t>
+          <t>3.43pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5489,12 +5489,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>4.00pm</t>
+          <t>3.43pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.30pm</t>
+          <t>4.13pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5507,75 +5507,75 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.30pm</t>
+          <t>4.13pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
+          <t>5.13pm</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>5.13pm</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
           <t>5.30pm</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>5.30pm</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>7.00pm</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>AN EVENING OF KECAK - INAUGURAL PUBLIC PERFORMANCE</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>Performance · Orion Mall, Rajajinagar · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>7.00pm</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>7.20pm</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
+          <t>7.00pm</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
           <t>7.20pm</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>7.50pm</t>
-        </is>
-      </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr"/>
@@ -5583,20 +5583,38 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
+          <t>7.20pm</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
           <t>7.50pm</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>7.50pm</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>8.50pm</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>Dinner near Orion Mall</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>added: the plan has dinner back at the stay</t>
         </is>

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -784,11 +784,7 @@
           <t>9.50pm · Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>“Shadow Puppetry Performance”: arrives 1.51pm, 21 min late for the 120 min preparation. · Late night: lights out at 1.16am (+1).</t>
-        </is>
-      </c>
+      <c r="G10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -898,12 +894,12 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Lecture Demonstration 6.00pm</t>
+          <t>Lecture Demonstration 5.00pm</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>4.36pm</t>
+          <t>3.35pm</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -913,7 +909,7 @@
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>7.40pm · Dinner near Indian Music Experience Museum</t>
+          <t>6.40pm · Dinner near Indian Music Experience Museum</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -960,23 +956,35 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Sat, 10 Oct</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Rest day</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr"/>
-      <c r="D16" s="7" t="inlineStr"/>
-      <c r="E16" s="7" t="inlineStr"/>
-      <c r="F16" s="7" t="inlineStr"/>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>Rest day at the stay · no travel</t>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Show day</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Dance Movement Workshop - 2 4.00pm</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>2.30pm</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr"/>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>7.20pm · Dinner before leaving</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Dinner added before leaving the venue; the plan itself has dinner at the stay after the drive back.</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1347,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Lecture Demonstration 6.00pm</t>
+          <t>Lecture Demonstration 5.00pm</t>
         </is>
       </c>
     </row>
@@ -1375,12 +1383,12 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>4.36pm</t>
+          <t>3.35pm</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.50pm</t>
+          <t>4.50pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1390,19 +1398,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 04 · 37 km · typical traffic for the day · 10 min loading first</t>
+          <t>1 h 05 · 37 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.50pm</t>
+          <t>4.50pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1415,12 +1423,12 @@
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>7.30pm</t>
+          <t>6.30pm</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -1437,12 +1445,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>7.30pm</t>
+          <t>6.30pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>7.40pm</t>
+          <t>6.40pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1455,12 +1463,12 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
+          <t>6.40pm</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
           <t>7.40pm</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>8.40pm</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
@@ -1889,7 +1897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1915,14 +1923,14 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Rest day at the stay</t>
+          <t>Dance Movement Workshop - 2 4.00pm</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>• Rest day at the stay · no travel</t>
+          <t>• Dinner added before leaving the venue; the plan itself has dinner at the stay after the drive back.</t>
         </is>
       </c>
     </row>
@@ -1949,9 +1957,158 @@
       </c>
     </row>
     <row r="7">
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Rest day at the stay · no travel</t>
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>2.30pm</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>3.25pm</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>→ Leave the stay for MLA College, Malleswaram</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>travel time unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>3.25pm</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>3.35pm</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>3.35pm</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>3.45pm</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>3.45pm</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>4.00pm</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>4.00pm</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>7.00pm</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>DANCE MOVEMENT WORKSHOP - 2</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Workshop</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>7.00pm</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>7.05pm</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>7.05pm</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>7.20pm</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>7.20pm</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>8.20pm</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Dinner before leaving</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>added: the plan has dinner back at the stay</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4787,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 04 · 48 km · live traffic · 10 min loading first</t>
+          <t>1 h 04 · 51 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5358,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.21am</t>
+          <t>6.22am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5211,19 +5368,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>31 min · 25 km · live traffic · 10 min loading first</t>
+          <t>32 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.21am</t>
+          <t>6.22am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.31am</t>
+          <t>6.32am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5236,12 +5393,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.31am</t>
+          <t>6.32am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.46am</t>
+          <t>6.47am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5254,7 +5411,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.46am</t>
+          <t>6.47am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5454,7 +5611,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>3.13pm</t>
+          <t>3.12pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5464,19 +5621,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>28 min · 18 km · live traffic · 10 min loading first</t>
+          <t>27 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>3.13pm</t>
+          <t>3.12pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.43pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5489,12 +5646,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.43pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.13pm</t>
+          <t>4.12pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5507,12 +5664,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.13pm</t>
+          <t>4.12pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.13pm</t>
+          <t>5.12pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5525,7 +5682,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.13pm</t>
+          <t>5.12pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5635,7 +5792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5695,7 +5852,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>8.24am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5705,19 +5862,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>44 min · 28 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>38 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>8.24am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.34am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -5730,12 +5887,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.34am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.44am</t>
+          <t>8.38am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5748,12 +5905,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.44am</t>
+          <t>8.38am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.59am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5763,140 +5920,140 @@
       </c>
       <c r="D9" s="7" t="inlineStr"/>
     </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>8.53am</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>9.00am</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>9.00am</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>12.30pm</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>DANCE MOVEMENT WORKSHOP</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>Workshop · Drishti Art Centre, Sahakara Nagar · 25 artists</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>12.00pm</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>Lunch at the venue (packed)</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>12.30pm</t>
+          <t>12.00pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>12.35pm</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Lunch at the venue (packed)</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
+          <t>12.30pm</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
           <t>12.35pm</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>12.35pm</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>1.51pm</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>1.28pm</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>1 h 01 · 26 km · traffic, refreshed hourly</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>1.51pm</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>2.21pm</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr"/>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>38 min · 26 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>2.21pm</t>
+          <t>1.28pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.51pm</t>
+          <t>1.58pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr"/>
@@ -5904,118 +6061,154 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.51pm</t>
+          <t>1.58pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
+          <t>2.28pm</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>2.28pm</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>3.28pm</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>3.28pm</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>5.00pm</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
         </is>
       </c>
-      <c r="D18" s="10" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>10.50pm</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr"/>
+      <c r="D24" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6187,7 +6380,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>52 min · 30 km · typical traffic for the day · 10 min loading first</t>
+          <t>52 min · 30 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -784,7 +784,11 @@
           <t>9.50pm · Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>“Shadow Puppetry Performance”: arrives 1.40pm, 10 min late for the 120 min preparation. · Late night: lights out at 1.03am (+1).</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -4777,7 +4781,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4787,19 +4791,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 04 · 51 km · live traffic · 10 min loading first</t>
+          <t>1 h 08 · 48 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.33pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.59pm</t>
+          <t>7.03pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5358,7 +5362,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.22am</t>
+          <t>6.21am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5368,19 +5372,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>32 min · 25 km · live traffic · 10 min loading first</t>
+          <t>31 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.22am</t>
+          <t>6.21am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.32am</t>
+          <t>6.31am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5393,12 +5397,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.32am</t>
+          <t>6.31am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.47am</t>
+          <t>6.46am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5411,7 +5415,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.47am</t>
+          <t>6.46am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5611,7 +5615,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>3.12pm</t>
+          <t>3.17pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5621,19 +5625,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>27 min · 18 km · live traffic · 10 min loading first</t>
+          <t>32 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>3.12pm</t>
+          <t>3.17pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.47pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5646,12 +5650,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.47pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.12pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5664,12 +5668,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.12pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.12pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5682,7 +5686,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.12pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5792,7 +5796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5852,7 +5856,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.24am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5862,19 +5866,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>38 min · 24 km · live traffic · 10 min loading first</t>
+          <t>44 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.24am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.28am</t>
+          <t>8.34am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -5887,12 +5891,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.28am</t>
+          <t>8.34am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.38am</t>
+          <t>8.44am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5905,12 +5909,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.38am</t>
+          <t>8.44am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>8.59am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5920,140 +5924,140 @@
       </c>
       <c r="D9" s="7" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>8.53am</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>9.00am</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>9.00am</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>12.30pm</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>DANCE MOVEMENT WORKSHOP</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>Workshop · Drishti Art Centre, Sahakara Nagar · 25 artists</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>12.00pm</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Lunch at the venue (packed)</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>12.00pm</t>
+          <t>12.30pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>Lunch at the venue (packed)</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
-        </is>
-      </c>
+          <t>12.35pm</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>12.30pm</t>
+          <t>12.35pm</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>12.35pm</t>
+          <t>12.50pm</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>12.35pm</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr"/>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>1.40pm</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>50 min · 29 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>12.50pm</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>1.28pm</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>38 min · 26 km · live traffic</t>
-        </is>
-      </c>
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>1.40pm</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>2.10pm</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.28pm</t>
+          <t>2.10pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>1.58pm</t>
+          <t>2.40pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr"/>
@@ -6061,154 +6065,118 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>1.58pm</t>
+          <t>2.40pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr"/>
     </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>2.28pm</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>3.28pm</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>3.28pm</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>3.30pm</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>5.00pm</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D18" s="10" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D19" s="10" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6610,7 +6578,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>54 min · 30 km · typical traffic for the day · 10 min loading first</t>
+          <t>54 min · 30 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -784,11 +784,7 @@
           <t>9.50pm · Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>“Shadow Puppetry Performance”: arrives 1.40pm, 10 min late for the 120 min preparation. · Late night: lights out at 1.03am (+1).</t>
-        </is>
-      </c>
+      <c r="G10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -829,7 +825,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>4.23pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1402,7 +1398,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 05 · 37 km · typical traffic for the day · 10 min loading first</t>
+          <t>1 h 05 · 37 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4777,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.33pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4791,19 +4787,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 08 · 48 km · live traffic · 10 min loading first</t>
+          <t>1 h 05 · 50 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.33pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>7.03pm</t>
+          <t>7.00pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5362,7 +5358,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.21am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5372,19 +5368,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>31 min · 25 km · live traffic · 10 min loading first</t>
+          <t>33 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.21am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.31am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5397,12 +5393,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.31am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.46am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5415,7 +5411,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.46am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5615,7 +5611,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>3.17pm</t>
+          <t>3.13pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5625,19 +5621,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>32 min · 18 km · live traffic · 10 min loading first</t>
+          <t>28 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>3.17pm</t>
+          <t>3.13pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.47pm</t>
+          <t>3.43pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5650,12 +5646,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.47pm</t>
+          <t>3.43pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.13pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5668,12 +5664,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.13pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.13pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5686,7 +5682,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.13pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5796,7 +5792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5856,7 +5852,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>8.24am</t>
+          <t>8.19am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5866,19 +5862,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>44 min · 26 km · live traffic · 10 min loading first</t>
+          <t>39 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>8.24am</t>
+          <t>8.19am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.34am</t>
+          <t>8.29am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -5891,12 +5887,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.34am</t>
+          <t>8.29am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.44am</t>
+          <t>8.39am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5909,12 +5905,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.44am</t>
+          <t>8.39am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.59am</t>
+          <t>8.54am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5924,140 +5920,140 @@
       </c>
       <c r="D9" s="7" t="inlineStr"/>
     </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>8.54am</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>9.00am</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>9.00am</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>12.30pm</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>DANCE MOVEMENT WORKSHOP</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>Workshop · Drishti Art Centre, Sahakara Nagar · 25 artists</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>12.00pm</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>Lunch at the venue (packed)</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>12.30pm</t>
+          <t>12.00pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>12.35pm</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Lunch at the venue (packed)</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
+          <t>12.30pm</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
           <t>12.35pm</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>12.35pm</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>1.40pm</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>1.33pm</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>50 min · 29 km · live traffic</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>1.40pm</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>2.10pm</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr"/>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>43 min · 29 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>2.10pm</t>
+          <t>1.33pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.40pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr"/>
@@ -6065,97 +6061,97 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.40pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
+          <t>2.33pm</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>2.33pm</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>3.30pm</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="D18" s="7" t="inlineStr"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
+          <t>3.30pm</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr"/>
@@ -6163,20 +6159,38 @@
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>10.50pm</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C23" s="15" t="inlineStr">
         <is>
           <t>Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr"/>
+      <c r="D23" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6271,7 +6285,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6333,12 +6347,12 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>4.23pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.25pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6348,19 +6362,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>52 min · 30 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>41 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.25pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.35pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6373,12 +6387,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.35pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.45pm</t>
+          <t>5.41pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6391,75 +6405,75 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.45pm</t>
+          <t>5.41pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
+          <t>5.56pm</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>5.56pm</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>KECAK WORKSHOP</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>Workshop · PCPA (Prestige Centre for Performing Arts), Konanakunte, Kanakapura Road · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>9.05pm</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
           <t>9.05pm</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr"/>
@@ -6467,20 +6481,38 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
+          <t>9.05pm</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>10.20pm</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>Dinner near PCPA (Prestige Centre for Performing Arts)</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>added: the plan has dinner back at the stay</t>
         </is>

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -862,7 +862,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>4.21pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>3.35pm</t>
+          <t>3.34pm</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1383,7 +1383,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>3.35pm</t>
+          <t>3.34pm</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 05 · 37 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>1 h 06 · 37 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>46 min · 28 km · typical traffic for the day · 10 min loading first</t>
+          <t>46 min · 28 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>14 min · 5 km · typical traffic for the day</t>
+          <t>14 min · 5 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -4777,7 +4777,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4787,19 +4787,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 05 · 50 km · live traffic · 10 min loading first</t>
+          <t>1 h 07 · 48 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>7.00pm</t>
+          <t>7.02pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>9.35pm</t>
+          <t>9.37pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5151,14 +5151,14 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>1 h 21 · 53 km · typical traffic for the day</t>
+          <t>1 h 23 · 53 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.35pm</t>
+          <t>9.37pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>3.13pm</t>
+          <t>3.14pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5621,19 +5621,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>28 min · 18 km · live traffic · 10 min loading first</t>
+          <t>29 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>3.13pm</t>
+          <t>3.14pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.43pm</t>
+          <t>3.44pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5646,12 +5646,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.43pm</t>
+          <t>3.44pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.13pm</t>
+          <t>4.14pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5664,12 +5664,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.13pm</t>
+          <t>4.14pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.13pm</t>
+          <t>5.14pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5682,7 +5682,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.13pm</t>
+          <t>5.14pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>8.19am</t>
+          <t>8.21am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5862,19 +5862,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>39 min · 24 km · live traffic · 10 min loading first</t>
+          <t>41 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>8.19am</t>
+          <t>8.21am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.29am</t>
+          <t>8.31am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -5887,12 +5887,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.29am</t>
+          <t>8.31am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.39am</t>
+          <t>8.41am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5905,12 +5905,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.39am</t>
+          <t>8.41am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.54am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5923,7 +5923,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.54am</t>
+          <t>8.56am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6036,19 +6036,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>43 min · 29 km · live traffic</t>
+          <t>44 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>2.04pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6061,12 +6061,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>2.04pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.34pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6079,7 +6079,7 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.34pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.22pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6362,19 +6362,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>41 min · 26 km · live traffic · 10 min loading first</t>
+          <t>42 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.22pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6387,12 +6387,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.41pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6405,12 +6405,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.41pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.56pm</t>
+          <t>5.57pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6423,7 +6423,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.56pm</t>
+          <t>5.57pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6533,7 +6533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6595,12 +6595,12 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>4.21pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.25pm</t>
+          <t>5.22pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6610,19 +6610,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>54 min · 30 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>42 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.25pm</t>
+          <t>5.22pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.35pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6635,12 +6635,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.35pm</t>
+          <t>5.32pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.45pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6653,75 +6653,75 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.45pm</t>
+          <t>5.42pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
+          <t>5.57pm</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>5.57pm</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>KECAK WORKSHOP</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>Workshop · PCPA (Prestige Centre for Performing Arts), Konanakunte, Kanakapura Road · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>9.05pm</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
           <t>9.05pm</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr"/>
@@ -6729,20 +6729,38 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
+          <t>9.05pm</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>10.20pm</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C15" s="15" t="inlineStr">
         <is>
           <t>Dinner near PCPA (Prestige Centre for Performing Arts)</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>added: the plan has dinner back at the stay</t>
         </is>

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -784,7 +784,11 @@
           <t>9.50pm · Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>“Shadow Puppetry Performance”: arrives 1.36pm, 6 min late for the 120 min preparation. · Late night: lights out at 1.01am (+1).</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -899,7 +903,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>3.34pm</t>
+          <t>3.55pm</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1383,7 +1387,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>3.34pm</t>
+          <t>3.55pm</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
@@ -1398,7 +1402,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 06 · 37 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>45 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -4777,7 +4781,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4787,19 +4791,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 07 · 48 km · live traffic · 10 min loading first</t>
+          <t>1 h 06 · 51 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>7.02pm</t>
+          <t>7.01pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5358,7 +5362,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.22am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5368,19 +5372,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>33 min · 25 km · live traffic · 10 min loading first</t>
+          <t>32 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.22am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.32am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5393,12 +5397,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.32am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.47am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5411,7 +5415,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.47am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5611,7 +5615,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>3.14pm</t>
+          <t>3.15pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5621,19 +5625,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>29 min · 18 km · live traffic · 10 min loading first</t>
+          <t>30 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>3.14pm</t>
+          <t>3.15pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.44pm</t>
+          <t>3.45pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5646,12 +5650,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.44pm</t>
+          <t>3.45pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.14pm</t>
+          <t>4.15pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5664,12 +5668,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.14pm</t>
+          <t>4.15pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.14pm</t>
+          <t>5.15pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5682,7 +5686,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.14pm</t>
+          <t>5.15pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5852,7 +5856,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>8.21am</t>
+          <t>8.22am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5862,19 +5866,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>41 min · 24 km · live traffic · 10 min loading first</t>
+          <t>42 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>8.21am</t>
+          <t>8.22am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.31am</t>
+          <t>8.32am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -5887,12 +5891,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.31am</t>
+          <t>8.32am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.41am</t>
+          <t>8.42am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5905,12 +5909,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.41am</t>
+          <t>8.42am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5923,7 +5927,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.56am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -6026,7 +6030,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.36pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6036,19 +6040,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>44 min · 26 km · live traffic</t>
+          <t>46 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.36pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.04pm</t>
+          <t>2.06pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6061,12 +6065,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.04pm</t>
+          <t>2.06pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.34pm</t>
+          <t>2.36pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6079,7 +6083,7 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.34pm</t>
+          <t>2.36pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
@@ -6352,7 +6356,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.22pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6362,19 +6366,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>42 min · 26 km · live traffic · 10 min loading first</t>
+          <t>41 min · 30 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.22pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6387,12 +6391,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.41pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6405,12 +6409,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.41pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.57pm</t>
+          <t>5.56pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6423,7 +6427,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.57pm</t>
+          <t>5.56pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6600,7 +6604,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.22pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6610,19 +6614,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>42 min · 26 km · live traffic · 10 min loading first</t>
+          <t>41 min · 30 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.22pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6635,12 +6639,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.32pm</t>
+          <t>5.31pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.41pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6653,12 +6657,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.42pm</t>
+          <t>5.41pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.57pm</t>
+          <t>5.56pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6671,7 +6675,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.57pm</t>
+          <t>5.56pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -784,11 +784,7 @@
           <t>9.50pm · Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>“Shadow Puppetry Performance”: arrives 1.36pm, 6 min late for the 120 min preparation. · Late night: lights out at 1.01am (+1).</t>
-        </is>
-      </c>
+      <c r="G10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -940,7 +936,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>8.29am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1325,7 +1321,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1392,7 +1388,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4.50pm</t>
+          <t>4.48pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1402,85 +1398,103 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>45 min · 27 km · live traffic · 10 min loading first</t>
+          <t>43 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>4.50pm</t>
+          <t>4.48pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
+          <t>4.58pm</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>4.58pm</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
           <t>5.00pm</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Sound check</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>5.00pm</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>6.30pm</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>LECTURE DEMONSTRATION</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>Talk · Indian Music Experience Museum, JP Nagar 7th Phase · 2 artists</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>6.30pm</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>6.40pm</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
+          <t>6.30pm</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
           <t>6.40pm</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>6.40pm</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>7.40pm</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>Dinner near Indian Music Experience Museum</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>added: the plan has dinner back at the stay</t>
         </is>
@@ -1501,7 +1515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1563,12 +1577,12 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>8.29am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1578,19 +1592,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>46 min · 28 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>34 min · 22 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1603,12 +1617,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.45am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1621,75 +1635,75 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.45am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
+          <t>9.49am</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>9.49am</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
           <t>10.00am</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>10.00am</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>1.00pm</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>WORKSHOP FOR STUDENTS</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>Workshop · Kumarans School, Chikkalasandra · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>1.05pm</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
           <t>1.05pm</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>1.20pm</t>
-        </is>
-      </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr"/>
@@ -1697,17 +1711,17 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
+          <t>1.05pm</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
           <t>1.20pm</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>2.46pm</t>
-        </is>
-      </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Hold in town near Kumarans School</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr"/>
@@ -1720,70 +1734,70 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
+          <t>2.50pm</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Hold in town near Kumarans School</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>1.20pm</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
           <t>2.20pm</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>Lunch near Kumarans School</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>2.46pm</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>2.50pm</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>3.00pm</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>→ Leave Kumarans School for Meenakshi Rangamancha</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>14 min · 5 km · traffic, refreshed hourly</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>3.00pm</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>3.30pm</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr"/>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>10 min · 5 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
+          <t>3.00pm</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>4.00pm</t>
-        </is>
-      </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr"/>
@@ -1791,75 +1805,75 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
+          <t>3.30pm</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
           <t>4.00pm</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>4.00pm</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>5.00pm</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>5.00pm</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>6.30pm</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>TRADITIONAL BALINESE DANCE</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>Performance · Meenakshi Rangamancha, Doddakallasandra, Kanakapura Road · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>6.30pm</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>6.50pm</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
+          <t>6.30pm</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
           <t>6.50pm</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>7.20pm</t>
-        </is>
-      </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
@@ -1867,20 +1881,38 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
+          <t>6.50pm</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
           <t>7.20pm</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>7.20pm</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>8.20pm</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>Dinner near Meenakshi Rangamancha</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="D24" s="18" t="inlineStr">
         <is>
           <t>added: the plan has dinner back at the stay</t>
         </is>
@@ -2198,7 +2230,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2208,19 +2240,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>31 min · 25 km · typical traffic for the day · 10 min loading first</t>
+          <t>32 min · 25 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.22am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2233,12 +2265,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.22am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2251,12 +2283,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.46am</t>
+          <t>9.47am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2269,7 +2301,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.46am</t>
+          <t>9.47am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2396,7 +2428,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>17 min · 5 km · typical traffic for the day</t>
+          <t>17 min · 5 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4813,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4791,19 +4823,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 06 · 51 km · live traffic · 10 min loading first</t>
+          <t>1 h 05 · 49 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>7.01pm</t>
+          <t>7.00pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5615,7 +5647,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>3.15pm</t>
+          <t>3.13pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5625,19 +5657,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>30 min · 18 km · live traffic · 10 min loading first</t>
+          <t>28 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>3.15pm</t>
+          <t>3.13pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.45pm</t>
+          <t>3.43pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5650,12 +5682,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.45pm</t>
+          <t>3.43pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.15pm</t>
+          <t>4.13pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5668,12 +5700,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.15pm</t>
+          <t>4.13pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.15pm</t>
+          <t>5.13pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5686,7 +5718,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.15pm</t>
+          <t>5.13pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5856,7 +5888,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>8.22am</t>
+          <t>8.20am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5866,19 +5898,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>42 min · 24 km · live traffic · 10 min loading first</t>
+          <t>40 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>8.22am</t>
+          <t>8.20am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.32am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -5891,12 +5923,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.32am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.42am</t>
+          <t>8.40am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5909,12 +5941,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.42am</t>
+          <t>8.40am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.55am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5927,7 +5959,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.55am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -6030,7 +6062,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.36pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6040,19 +6072,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>46 min · 26 km · live traffic</t>
+          <t>44 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.36pm</t>
+          <t>1.34pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.06pm</t>
+          <t>2.04pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6065,12 +6097,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.06pm</t>
+          <t>2.04pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.36pm</t>
+          <t>2.34pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6083,7 +6115,7 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.36pm</t>
+          <t>2.34pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -1388,7 +1388,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4.48pm</t>
+          <t>4.47pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1398,19 +1398,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>43 min · 27 km · live traffic · 10 min loading first</t>
+          <t>42 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>4.48pm</t>
+          <t>4.47pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>4.58pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1423,7 +1423,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>4.58pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1592,19 +1592,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>34 min · 22 km · live traffic · 10 min loading first</t>
+          <t>33 min · 22 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1617,12 +1617,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1653,7 +1653,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2658,19 +2658,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>34 min · 25 km · typical traffic for the day · 10 min loading first</t>
+          <t>35 min · 25 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2683,12 +2683,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2701,12 +2701,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2719,7 +2719,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4823,19 +4823,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 05 · 49 km · live traffic · 10 min loading first</t>
+          <t>1 h 04 · 48 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>7.00pm</t>
+          <t>6.59pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>3.13pm</t>
+          <t>3.12pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5657,19 +5657,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>28 min · 18 km · live traffic · 10 min loading first</t>
+          <t>27 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>3.13pm</t>
+          <t>3.12pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.43pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5682,12 +5682,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.43pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.13pm</t>
+          <t>4.12pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5700,12 +5700,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.13pm</t>
+          <t>4.12pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.13pm</t>
+          <t>5.12pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5718,7 +5718,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.13pm</t>
+          <t>5.12pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5888,7 +5888,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>8.20am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5898,19 +5898,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>40 min · 24 km · live traffic · 10 min loading first</t>
+          <t>38 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>8.20am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.30am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -5923,12 +5923,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.30am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.40am</t>
+          <t>8.38am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5941,12 +5941,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.40am</t>
+          <t>8.38am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.55am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5959,7 +5959,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.55am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.33pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6072,19 +6072,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>44 min · 29 km · live traffic</t>
+          <t>43 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.34pm</t>
+          <t>1.33pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.04pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6097,12 +6097,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.04pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.34pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6115,7 +6115,7 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.34pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
@@ -6398,7 +6398,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>41 min · 30 km · live traffic · 10 min loading first</t>
+          <t>41 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -6646,7 +6646,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>41 min · 30 km · live traffic · 10 min loading first</t>
+          <t>41 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -1734,7 +1734,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1765,7 +1765,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>10 min · 5 km · live traffic</t>
+          <t>11 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.12am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2240,19 +2240,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>32 min · 25 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>33 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.12am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.22am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2265,12 +2265,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.22am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2283,12 +2283,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.47am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2301,7 +2301,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.47am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>3.06pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -2413,12 +2413,12 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>3.06pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>3.14pm</t>
+          <t>3.15pm</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -2428,19 +2428,19 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>17 min · 5 km · traffic, refreshed hourly</t>
+          <t>9 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>3.14pm</t>
+          <t>3.15pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>3.59pm</t>
+          <t>4.00pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -2453,12 +2453,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>3.59pm</t>
+          <t>4.00pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>4.29pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -2471,12 +2471,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>4.29pm</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -3083,7 +3083,7 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>50 min · 27 km · typical traffic for the day · 10 min loading first</t>
+          <t>50 min · 27 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>4.16pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -3487,7 +3487,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>4.16pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -3502,7 +3502,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>9 min · 2 km · typical traffic for the day</t>
+          <t>8 min · 2 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 04 · 48 km · live traffic · 10 min loading first</t>
+          <t>1 h 04 · 51 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5394,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.22am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5404,19 +5404,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>32 min · 25 km · live traffic · 10 min loading first</t>
+          <t>33 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.22am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.32am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5429,12 +5429,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.32am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.47am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5447,7 +5447,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.47am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>3.12pm</t>
+          <t>3.13pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5657,19 +5657,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>27 min · 18 km · live traffic · 10 min loading first</t>
+          <t>28 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>3.12pm</t>
+          <t>3.13pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.43pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5682,12 +5682,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.43pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.12pm</t>
+          <t>4.13pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5700,12 +5700,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.12pm</t>
+          <t>4.13pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.12pm</t>
+          <t>5.13pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5718,7 +5718,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.12pm</t>
+          <t>5.13pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.29pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6072,19 +6072,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>43 min · 29 km · live traffic</t>
+          <t>39 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.29pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>1.59pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6097,12 +6097,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>1.59pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.29pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6115,12 +6115,12 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.29pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>3.29pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6398,19 +6398,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>41 min · 26 km · live traffic · 10 min loading first</t>
+          <t>40 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6423,12 +6423,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.41pm</t>
+          <t>5.40pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6441,12 +6441,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.41pm</t>
+          <t>5.40pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.56pm</t>
+          <t>5.55pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6459,7 +6459,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.56pm</t>
+          <t>5.55pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6636,7 +6636,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6646,19 +6646,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>41 min · 26 km · live traffic · 10 min loading first</t>
+          <t>40 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6671,12 +6671,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.31pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.41pm</t>
+          <t>5.40pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6689,12 +6689,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.41pm</t>
+          <t>5.40pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.56pm</t>
+          <t>5.55pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6707,7 +6707,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.56pm</t>
+          <t>5.55pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -771,7 +771,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>7.30am</t>
+          <t>7.29am</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -784,7 +784,11 @@
           <t>9.50pm · Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>“Shadow Puppetry Performance”: arrives 1.43pm, 13 min late for the 120 min preparation. · Late night: lights out at 1.07am (+1).</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -899,7 +903,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>3.55pm</t>
+          <t>3.49pm</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1321,7 +1325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1383,12 +1387,12 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>3.55pm</t>
+          <t>3.49pm</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4.47pm</t>
+          <t>4.50pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1398,19 +1402,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>42 min · 27 km · live traffic · 10 min loading first</t>
+          <t>51 min · 37 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>4.47pm</t>
+          <t>4.50pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>4.57pm</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1420,81 +1424,63 @@
       </c>
       <c r="D8" s="7" t="inlineStr"/>
     </row>
-    <row r="9">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>4.57pm</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>5.00pm</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>6.30pm</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>LECTURE DEMONSTRATION</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>Talk · Indian Music Experience Museum, JP Nagar 7th Phase · 2 artists</t>
         </is>
       </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>6.30pm</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>6.40pm</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.30pm</t>
+          <t>6.40pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>6.40pm</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>6.40pm</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
           <t>7.40pm</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>Dinner near Indian Music Experience Museum</t>
         </is>
       </c>
-      <c r="D12" s="18" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
         <is>
           <t>added: the plan has dinner back at the stay</t>
         </is>
@@ -1582,7 +1568,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1592,19 +1578,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>33 min · 22 km · live traffic · 10 min loading first</t>
+          <t>39 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1617,12 +1603,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.39am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1635,12 +1621,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.39am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.54am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1653,7 +1639,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.54am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -1734,7 +1720,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.48pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1765,7 +1751,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.48pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -1780,7 +1766,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>11 min · 5 km · live traffic</t>
+          <t>12 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2230,7 +2216,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2240,19 +2226,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>33 min · 25 km · live traffic · 10 min loading first</t>
+          <t>29 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2265,12 +2251,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2283,12 +2269,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2301,7 +2287,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2382,7 +2368,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>3.06pm</t>
+          <t>3.05pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -2413,7 +2399,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>3.06pm</t>
+          <t>3.05pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -2428,7 +2414,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>9 min · 5 km · live traffic</t>
+          <t>10 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2634,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2658,19 +2644,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>35 min · 25 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>29 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2683,12 +2669,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2701,12 +2687,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2719,7 +2705,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3314,7 +3300,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>58 min · 35 km · typical traffic for the day · 10 min loading first</t>
+          <t>58 min · 35 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3488,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>8 min · 2 km · typical traffic for the day</t>
+          <t>8 min · 2 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4799,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.35pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4823,19 +4809,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 04 · 51 km · live traffic · 10 min loading first</t>
+          <t>1 h 10 · 51 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.35pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.59pm</t>
+          <t>7.05pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5394,7 +5380,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.19am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5404,19 +5390,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>33 min · 25 km · live traffic · 10 min loading first</t>
+          <t>29 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.19am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.29am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5429,12 +5415,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.29am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.44am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5447,7 +5433,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.44am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5647,7 +5633,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>3.13pm</t>
+          <t>3.20pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5657,19 +5643,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>28 min · 18 km · live traffic · 10 min loading first</t>
+          <t>35 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>3.13pm</t>
+          <t>3.20pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.43pm</t>
+          <t>3.50pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5682,12 +5668,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.43pm</t>
+          <t>3.50pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.13pm</t>
+          <t>4.20pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5700,12 +5686,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.13pm</t>
+          <t>4.20pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.13pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5718,7 +5704,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.13pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5828,7 +5814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5883,12 +5869,12 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>7.30am</t>
+          <t>7.29am</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.25am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5898,19 +5884,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>38 min · 24 km · live traffic · 10 min loading first</t>
+          <t>46 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.25am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.28am</t>
+          <t>8.35am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -5923,12 +5909,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.28am</t>
+          <t>8.35am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.38am</t>
+          <t>8.45am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5941,12 +5927,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.38am</t>
+          <t>8.45am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>9.00am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5956,140 +5942,140 @@
       </c>
       <c r="D9" s="7" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>8.53am</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>9.00am</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>9.00am</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>12.30pm</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>DANCE MOVEMENT WORKSHOP</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>Workshop · Drishti Art Centre, Sahakara Nagar · 25 artists</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>12.00pm</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="C11" s="15" t="inlineStr">
+        <is>
+          <t>Lunch at the venue (packed)</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>12.00pm</t>
+          <t>12.30pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>Lunch at the venue (packed)</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
-        </is>
-      </c>
+          <t>12.35pm</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>12.30pm</t>
+          <t>12.35pm</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>12.35pm</t>
+          <t>12.50pm</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>12.35pm</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr"/>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>1.43pm</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>53 min · 26 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>12.50pm</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>1.29pm</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="inlineStr">
-        <is>
-          <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>39 min · 26 km · live traffic</t>
-        </is>
-      </c>
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>1.43pm</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>2.13pm</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.29pm</t>
+          <t>2.13pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>1.59pm</t>
+          <t>2.43pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr"/>
@@ -6097,53 +6083,57 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>1.59pm</t>
+          <t>2.43pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.29pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr"/>
     </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>2.29pm</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>3.29pm</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr"/>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>3.30pm</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
@@ -6152,42 +6142,38 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr"/>
@@ -6195,38 +6181,20 @@
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C23" s="15" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6398,7 +6366,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>40 min · 26 km · live traffic · 10 min loading first</t>
+          <t>40 min · 30 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -6646,7 +6614,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>40 min · 26 km · live traffic · 10 min loading first</t>
+          <t>40 min · 30 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -771,7 +771,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>7.29am</t>
+          <t>7.30am</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -784,11 +784,7 @@
           <t>9.50pm · Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>“Shadow Puppetry Performance”: arrives 1.43pm, 13 min late for the 120 min preparation. · Late night: lights out at 1.07am (+1).</t>
-        </is>
-      </c>
+      <c r="G10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -903,7 +899,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>3.49pm</t>
+          <t>3.55pm</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1084,7 +1080,7 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>3.00pm</t>
+          <t>3.05pm</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -1121,7 +1117,7 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>8.15am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -1158,7 +1154,7 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>8.15am</t>
+          <t>8.14am</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -1264,27 +1260,23 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>Closing Day 11.00am</t>
+          <t>The Finale 6.30pm</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>9.34am</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>Sabha Bengaluru</t>
-        </is>
-      </c>
+          <t>3.35pm</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr"/>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>10.10pm · Dinner near Sabha Bengaluru (late return)</t>
+          <t>8.50pm · Dinner before leaving</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>2 of 25 artists travel today; 23 stay at the stay. · Late night: lights out at 1.07am (+1).</t>
+          <t>Dinner added before leaving the venue; the plan itself has dinner at the stay after the drive back.</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1387,12 +1379,12 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>3.49pm</t>
+          <t>3.55pm</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4.50pm</t>
+          <t>4.45pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1402,85 +1394,103 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>51 min · 37 km · live traffic · 10 min loading first</t>
+          <t>40 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>4.50pm</t>
+          <t>4.45pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
+          <t>4.55pm</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>4.55pm</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
           <t>5.00pm</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Sound check</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr"/>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>5.00pm</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>6.30pm</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>LECTURE DEMONSTRATION</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>Talk · Indian Music Experience Museum, JP Nagar 7th Phase · 2 artists</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>6.30pm</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>6.40pm</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
+          <t>6.30pm</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
           <t>6.40pm</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>6.40pm</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
         <is>
           <t>7.40pm</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C12" s="15" t="inlineStr">
         <is>
           <t>Dinner near Indian Music Experience Museum</t>
         </is>
       </c>
-      <c r="D11" s="18" t="inlineStr">
+      <c r="D12" s="18" t="inlineStr">
         <is>
           <t>added: the plan has dinner back at the stay</t>
         </is>
@@ -1568,7 +1578,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1578,19 +1588,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>39 min · 25 km · live traffic · 10 min loading first</t>
+          <t>32 min · 22 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.22am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1603,12 +1613,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.22am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.39am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1621,12 +1631,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.39am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.54am</t>
+          <t>9.47am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1639,7 +1649,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.54am</t>
+          <t>9.47am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -1720,7 +1730,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>2.48pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1751,7 +1761,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>2.48pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -1766,7 +1776,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>12 min · 5 km · live traffic</t>
+          <t>10 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2226,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2226,19 +2236,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>29 min · 25 km · live traffic · 10 min loading first</t>
+          <t>34 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2251,12 +2261,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2269,12 +2279,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2287,7 +2297,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2368,7 +2378,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>3.05pm</t>
+          <t>3.06pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -2399,7 +2409,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>3.05pm</t>
+          <t>3.06pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -2414,7 +2424,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>10 min · 5 km · live traffic</t>
+          <t>9 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2634,7 +2644,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2644,19 +2654,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>29 min · 25 km · live traffic · 10 min loading first</t>
+          <t>34 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2669,12 +2679,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2687,12 +2697,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2705,7 +2715,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2985,7 +2995,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3054,12 +3064,12 @@
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>3.00pm</t>
+          <t>3.05pm</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>4.00pm</t>
+          <t>3.49pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -3069,19 +3079,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>50 min · 27 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>34 min · 22 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>4.00pm</t>
+          <t>3.49pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.30pm</t>
+          <t>4.19pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3094,12 +3104,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.30pm</t>
+          <t>4.19pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>4.49pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3112,75 +3122,75 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>4.49pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
+          <t>5.49pm</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>5.49pm</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>6.00pm</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>TRADITIONAL BALINESE DANCE × YAKSHAGANA PERFORMANCE</t>
         </is>
       </c>
-      <c r="D12" s="10" t="inlineStr">
+      <c r="D13" s="10" t="inlineStr">
         <is>
           <t>Performance · Chowdiah Memorial Hall, Vyalikaval, Malleshwaram · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>7.50pm</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
+          <t>7.30pm</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
           <t>7.50pm</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>8.20pm</t>
-        </is>
-      </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr"/>
@@ -3188,20 +3198,38 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
+          <t>7.50pm</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
           <t>8.20pm</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>8.20pm</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>Dinner near Chowdiah Memorial Hall</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>added: the plan has dinner back at the stay</t>
         </is>
@@ -3285,12 +3313,12 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>8.15am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -3300,19 +3328,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>58 min · 35 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>35 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3325,12 +3353,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.43am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3343,12 +3371,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.43am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.58am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3361,7 +3389,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.58am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3442,7 +3470,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.21pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -3473,7 +3501,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.21pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -3488,7 +3516,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>8 min · 2 km · traffic, refreshed hourly</t>
+          <t>4 min · 2 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -3641,7 +3669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3696,12 +3724,12 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>8.15am</t>
+          <t>8.14am</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -3711,19 +3739,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>58 min · 35 km · typical traffic for the day · 10 min loading first</t>
+          <t>1 h · 35 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -3736,12 +3764,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.43am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3754,12 +3782,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.43am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.58am</t>
+          <t>9.59am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3769,176 +3797,176 @@
       </c>
       <c r="D9" s="7" t="inlineStr"/>
     </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>9.58am</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>10.00am</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>10.00am</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>1.00pm</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>MASK MAKING WORKSHOP</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>Workshop · PARSEC, Jayanagar (Maker's Adda), Jayanagar 7th Block · 25 artists</t>
         </is>
       </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="inlineStr">
+        <is>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>1.05pm</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>1.00pm</t>
+          <t>1.05pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>1.05pm</t>
+          <t>1.20pm</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>1.05pm</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>1.20pm</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr"/>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>2.18pm</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>→ Back to the stay</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>58 min · 24 km · traffic, refreshed hourly</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>1.20pm</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>2.17pm</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
-        <is>
-          <t>→ Back to the stay</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>57 min · 24 km · typical traffic for the day</t>
-        </is>
-      </c>
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>2.18pm</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>4.13pm</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>At the stay — rest</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>2.17pm</t>
+          <t>2.18pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>4.12pm</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>At the stay — rest</t>
+          <t>3.18pm</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>Lunch at the stay</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>2.17pm</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>3.17pm</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
-        <is>
-          <t>Lunch at the stay</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr"/>
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>4.13pm</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>5.30pm</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>→ Leave the stay for Yuvapatha</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>1 h 07 · 37 km · traffic, refreshed hourly · 10 min loading first</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>4.12pm</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>5.30pm</t>
         </is>
       </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>→ Leave the stay for Yuvapatha</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>1 h 08 · 37 km · typical traffic for the day · 10 min loading first</t>
-        </is>
-      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>6.00pm</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Instrument &amp; stage set-up</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>6.00pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>6.30pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Instrument &amp; stage set-up</t>
+          <t>Sound check</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr"/>
@@ -3946,75 +3974,75 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>6.30pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>6.30pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr"/>
     </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>6.30pm</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="inlineStr">
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>BALINESE SHADOW PUPPETRY PERFORMANCE</t>
         </is>
       </c>
-      <c r="D21" s="10" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>Performance · Yuvapatha, Jayanagar · 25 artists</t>
         </is>
       </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
+        <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
@@ -4022,17 +4050,17 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Dinner near Yuvapatha</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr"/>
@@ -4040,54 +4068,36 @@
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>10.50pm</t>
         </is>
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>Dinner near Yuvapatha</t>
+          <t>11.45pm</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Wait for the coach at Yuvapatha</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>11.45pm</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Wait for the coach at Yuvapatha</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
-        <is>
-          <t>11.45pm</t>
-        </is>
-      </c>
-      <c r="B26" s="11" t="inlineStr"/>
-      <c r="C26" s="12" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr"/>
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>→ Leave Yuvapatha for Manipal University — overnight drive</t>
         </is>
       </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>7 h 32 · 413 km · typical traffic for the day · sleep on the road</t>
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>7 h 32 · 413 km · traffic, refreshed hourly · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4186,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 32 · 413 km · typical traffic for the day · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 32 · 413 km · traffic, refreshed hourly · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
@@ -4382,7 +4392,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>7 h 48 · 378 km · typical traffic for the day · home about 5.32am (+1)</t>
+          <t>7 h 42 · 378 km · traffic, refreshed hourly · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4568,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>1.59pm</t>
+          <t>2.00pm</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -4568,19 +4578,19 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>1 h 07 · 37 km · typical traffic for the day · 10 min loading first</t>
+          <t>1 h 08 · 37 km · typical traffic for the day · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>1.59pm</t>
+          <t>2.00pm</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>2.29pm</t>
+          <t>2.30pm</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -4593,12 +4603,12 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>2.29pm</t>
+          <t>2.30pm</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>2.59pm</t>
+          <t>3.00pm</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -4611,12 +4621,12 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>2.59pm</t>
+          <t>3.00pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>3.59pm</t>
+          <t>4.00pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -4799,7 +4809,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.35pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4809,19 +4819,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 10 · 51 km · live traffic · 10 min loading first</t>
+          <t>1 h 02 · 51 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.35pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>7.05pm</t>
+          <t>6.57pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -4865,7 +4875,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4891,171 +4901,199 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Closing Day 11.00am</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+          <t>The Finale 6.30pm</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>• Dinner added before leaving the venue; the plan itself has dinner at the stay after the drive back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>From</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>What</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Where / detail</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>9.34am</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>10.48am</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>→ Leave the stay for Sabha Bengaluru</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>1 h 04 · 24 km · typical traffic for the day · 10 min loading first</t>
-        </is>
-      </c>
-    </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>10.48am</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>10.58am</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Sound check</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr"/>
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>3.35pm</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>4.30pm</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>→ Leave the stay for Suchitra Cinema and Cultural Academy - Amphitheatre</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>travel time unknown</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>10.58am</t>
+          <t>4.30pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>11.00am</t>
+          <t>5.00pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Spare time at the venue</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr"/>
     </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>11.00am</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>10.00pm</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>CLOSING DAY</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>Talk · Sabha Bengaluru, Shivajinagar · 2 artists</t>
-        </is>
-      </c>
+    <row r="9">
+      <c r="A9" s="14" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>5.30pm</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>12.00pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
-        <is>
-          <t>Lunch at the venue (packed)</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>During “Closing Day” — arrange packed lunch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>10.00pm</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>10.10pm</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr"/>
+          <t>6.30pm</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>6.30pm</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>8.00pm</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>THE FINALE</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>10.10pm</t>
+          <t>8.00pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>11.10pm</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
-        <is>
-          <t>Dinner near Sabha Bengaluru (late return)</t>
+          <t>8.20pm</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>8.20pm</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>8.50pm</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>8.50pm</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Dinner before leaving</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>added: the plan has dinner back at the stay</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A4:D4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5380,7 +5418,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.19am</t>
+          <t>6.24am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5390,19 +5428,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>29 min · 25 km · live traffic · 10 min loading first</t>
+          <t>34 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.19am</t>
+          <t>6.24am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.29am</t>
+          <t>6.34am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5415,12 +5453,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.29am</t>
+          <t>6.34am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.44am</t>
+          <t>6.49am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5433,7 +5471,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.44am</t>
+          <t>6.49am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5633,7 +5671,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>3.20pm</t>
+          <t>3.11pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5643,19 +5681,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>35 min · 18 km · live traffic · 10 min loading first</t>
+          <t>26 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>3.20pm</t>
+          <t>3.11pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.50pm</t>
+          <t>3.41pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5668,12 +5706,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.50pm</t>
+          <t>3.41pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.20pm</t>
+          <t>4.11pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5686,12 +5724,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.20pm</t>
+          <t>4.11pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.11pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5704,7 +5742,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.11pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5814,7 +5852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5869,12 +5907,12 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>7.29am</t>
+          <t>7.30am</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>8.25am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5884,19 +5922,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>46 min · 26 km · live traffic · 10 min loading first</t>
+          <t>37 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>8.25am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.35am</t>
+          <t>8.27am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -5909,12 +5947,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.35am</t>
+          <t>8.27am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.45am</t>
+          <t>8.37am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5927,155 +5965,155 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.45am</t>
+          <t>8.37am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
+          <t>8.52am</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>8.52am</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
           <t>9.00am</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr"/>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>9.00am</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>12.30pm</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>DANCE MOVEMENT WORKSHOP</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>Workshop · Drishti Art Centre, Sahakara Nagar · 25 artists</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>12.00pm</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>Lunch at the venue (packed)</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>12.30pm</t>
+          <t>12.00pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>12.35pm</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr"/>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>Lunch at the venue (packed)</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>During “Dance Movement Workshop” — arrange packed lunch.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
+          <t>12.30pm</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
           <t>12.35pm</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>12.35pm</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>12.50pm</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>1.43pm</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>1.31pm</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>→ Leave Drishti Art Centre for Jagriti Theatre</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>53 min · 26 km · live traffic</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>1.43pm</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>2.13pm</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr"/>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>41 min · 29 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>2.13pm</t>
+          <t>1.31pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.43pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr"/>
@@ -6083,97 +6121,97 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.43pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
+          <t>2.31pm</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>2.31pm</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>3.30pm</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
-        </is>
-      </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="D18" s="7" t="inlineStr"/>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
+          <t>3.30pm</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
-      <c r="D19" s="10" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr"/>
@@ -6181,20 +6219,38 @@
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>10.50pm</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C23" s="15" t="inlineStr">
         <is>
           <t>Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr"/>
+      <c r="D23" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6356,7 +6412,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6366,19 +6422,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>40 min · 30 km · live traffic · 10 min loading first</t>
+          <t>39 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6391,12 +6447,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6409,12 +6465,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.55pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6427,7 +6483,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.55pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6604,7 +6660,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6614,19 +6670,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>40 min · 30 km · live traffic · 10 min loading first</t>
+          <t>39 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6639,12 +6695,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6657,12 +6713,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.55pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6675,7 +6731,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.55pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -1154,7 +1154,7 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>8.14am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>7.17am</t>
+          <t>7.05am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4.45pm</t>
+          <t>4.46pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1394,19 +1394,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>40 min · 27 km · live traffic · 10 min loading first</t>
+          <t>41 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>4.45pm</t>
+          <t>4.46pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>4.55pm</t>
+          <t>4.56pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>4.55pm</t>
+          <t>4.56pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -3669,7 +3669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3724,12 +3724,12 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>8.14am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -3739,19 +3739,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>1 h · 35 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>35 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -3764,12 +3764,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3782,12 +3782,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.59am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3797,176 +3797,176 @@
       </c>
       <c r="D9" s="7" t="inlineStr"/>
     </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>9.50am</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>10.00am</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>10.00am</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>1.00pm</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>MASK MAKING WORKSHOP</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>Workshop · PARSEC, Jayanagar (Maker's Adda), Jayanagar 7th Block · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>1.00pm</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>1.05pm</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
+          <t>1.00pm</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
           <t>1.05pm</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>1.05pm</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>1.20pm</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>1.20pm</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>2.18pm</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>1.53pm</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>→ Back to the stay</t>
         </is>
       </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>58 min · 24 km · traffic, refreshed hourly</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>2.18pm</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>4.13pm</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>At the stay — rest</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr"/>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>33 min · 24 km · live traffic</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>2.18pm</t>
+          <t>1.53pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>3.18pm</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="inlineStr">
+          <t>4.41pm</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>At the stay — rest</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>1.53pm</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>2.53pm</t>
+        </is>
+      </c>
+      <c r="C16" s="15" t="inlineStr">
         <is>
           <t>Lunch at the stay</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>4.13pm</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>5.30pm</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>4.32pm</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>5.21pm</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>→ Leave the stay for Yuvapatha</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>1 h 07 · 37 km · traffic, refreshed hourly · 10 min loading first</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>5.30pm</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>6.00pm</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Instrument &amp; stage set-up</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr"/>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>39 min · 26 km · live traffic · 10 min loading first</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>6.00pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>6.30pm</t>
+          <t>5.51pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Sound check</t>
+          <t>Instrument &amp; stage set-up</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr"/>
@@ -3974,93 +3974,93 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>6.30pm</t>
+          <t>5.51pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>7.30pm</t>
+          <t>6.21pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
+          <t>Sound check</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>6.21pm</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>7.21pm</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
           <t>Costume, make-up, warm-up &amp; call</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="C20" s="9" t="inlineStr">
-        <is>
-          <t>BALINESE SHADOW PUPPETRY PERFORMANCE</t>
-        </is>
-      </c>
-      <c r="D20" s="10" t="inlineStr">
-        <is>
-          <t>Performance · Yuvapatha, Jayanagar · 25 artists</t>
-        </is>
-      </c>
+      <c r="D20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
+          <t>7.21pm</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>7.30pm</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>7.30pm</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr"/>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>BALINESE SHADOW PUPPETRY PERFORMANCE</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Performance · Yuvapatha, Jayanagar · 25 artists</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>9.50pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C23" s="15" t="inlineStr">
-        <is>
-          <t>Dinner near Yuvapatha</t>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr"/>
@@ -4068,36 +4068,72 @@
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
         <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
           <t>10.50pm</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Dinner near Yuvapatha</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="14" t="inlineStr">
+        <is>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
         <is>
           <t>11.45pm</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Wait for the coach at Yuvapatha</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>11.45pm</t>
         </is>
       </c>
-      <c r="B25" s="11" t="inlineStr"/>
-      <c r="C25" s="12" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr"/>
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>→ Leave Yuvapatha for Manipal University — overnight drive</t>
         </is>
       </c>
-      <c r="D25" s="13" t="inlineStr">
-        <is>
-          <t>7 h 32 · 413 km · traffic, refreshed hourly · sleep on the road</t>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>7 h 20 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>7.17am</t>
+          <t>7.05am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4186,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 32 · 413 km · traffic, refreshed hourly · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 20 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>7.17am</t>
+          <t>7.05am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.47am</t>
+          <t>8.35am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4211,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.47am</t>
+          <t>8.35am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.05am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4229,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.05am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.47am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4247,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.47am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4392,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>7 h 42 · 378 km · traffic, refreshed hourly · home about 5.32am (+1)</t>
+          <t>7 h 04 · 386 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4614,7 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>1 h 08 · 37 km · typical traffic for the day · 10 min loading first</t>
+          <t>1 h 08 · 37 km · traffic, refreshed hourly · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5237,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>9.37pm</t>
+          <t>9.36pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5211,14 +5247,14 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>1 h 23 · 53 km · typical traffic for the day</t>
+          <t>1 h 22 · 53 km · typical traffic for the day</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.37pm</t>
+          <t>9.36pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -5671,7 +5707,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>3.11pm</t>
+          <t>3.12pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5681,19 +5717,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>26 min · 18 km · live traffic · 10 min loading first</t>
+          <t>27 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>3.11pm</t>
+          <t>3.12pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.41pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5706,12 +5742,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.41pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.11pm</t>
+          <t>4.12pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5724,12 +5760,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.11pm</t>
+          <t>4.12pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.11pm</t>
+          <t>5.12pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5742,7 +5778,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.11pm</t>
+          <t>5.12pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5912,7 +5948,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5922,19 +5958,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>37 min · 24 km · live traffic · 10 min loading first</t>
+          <t>38 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.27am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -5947,12 +5983,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.27am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.37am</t>
+          <t>8.38am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5965,12 +6001,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.37am</t>
+          <t>8.38am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.52am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5983,7 +6019,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.52am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -6086,7 +6122,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.32pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6096,19 +6132,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>41 min · 29 km · live traffic</t>
+          <t>42 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.32pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>2.02pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6121,12 +6157,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>2.02pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.32pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6139,7 +6175,7 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.32pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>7.05am</t>
+          <t>7.12am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4.46pm</t>
+          <t>4.48pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1394,19 +1394,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>41 min · 27 km · live traffic · 10 min loading first</t>
+          <t>43 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>4.46pm</t>
+          <t>4.48pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>4.56pm</t>
+          <t>4.58pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>4.56pm</t>
+          <t>4.58pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.12am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1588,19 +1588,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>32 min · 22 km · live traffic · 10 min loading first</t>
+          <t>34 min · 22 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.12am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.22am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.22am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1631,12 +1631,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.47am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1649,7 +1649,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.47am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.48pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1761,7 +1761,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.48pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>10 min · 5 km · live traffic</t>
+          <t>12 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2236,19 +2236,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>34 min · 25 km · live traffic · 10 min loading first</t>
+          <t>31 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2261,12 +2261,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2279,12 +2279,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.46am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2297,7 +2297,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.46am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2654,19 +2654,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>34 min · 25 km · live traffic · 10 min loading first</t>
+          <t>31 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2679,12 +2679,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.46am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2715,7 +2715,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.46am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -3328,19 +3328,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>35 min · 24 km · live traffic · 10 min loading first</t>
+          <t>37 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3353,12 +3353,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.37am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.37am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.52am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3389,7 +3389,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.52am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -3739,19 +3739,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>35 min · 24 km · live traffic · 10 min loading first</t>
+          <t>37 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -3764,12 +3764,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.37am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3782,12 +3782,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.37am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.52am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3800,7 +3800,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.52am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>1.53pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -3891,19 +3891,19 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>33 min · 24 km · live traffic</t>
+          <t>35 min · 24 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>1.53pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>4.41pm</t>
+          <t>4.40pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -3916,12 +3916,12 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.53pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.53pm</t>
+          <t>2.55pm</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.22pm</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -3949,19 +3949,19 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic · 10 min loading first</t>
+          <t>40 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.22pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>5.51pm</t>
+          <t>5.52pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3974,12 +3974,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>5.51pm</t>
+          <t>5.52pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>6.21pm</t>
+          <t>6.22pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -3992,12 +3992,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>6.21pm</t>
+          <t>6.22pm</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>7.21pm</t>
+          <t>7.22pm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -4010,7 +4010,7 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>7.21pm</t>
+          <t>7.22pm</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 20 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 27 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>7.05am</t>
+          <t>7.12am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4222,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 20 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 27 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>7.05am</t>
+          <t>7.12am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.35am</t>
+          <t>8.42am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.35am</t>
+          <t>8.42am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.05am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.05am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.42am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.42am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>7 h 04 · 386 km · live traffic · home about 5.32am (+1)</t>
+          <t>6 h 57 · 387 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -4447,7 +4447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>12.12pm</t>
+          <t>12.35pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4581,12 +4581,12 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>12.12pm</t>
+          <t>12.35pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>12.42pm</t>
+          <t>1.05pm</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -4599,12 +4599,12 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>12.42pm</t>
+          <t>1.05pm</t>
         </is>
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>2.00pm</t>
+          <t>1.58pm</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -4614,19 +4614,19 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>1 h 08 · 37 km · traffic, refreshed hourly · 10 min loading first</t>
+          <t>43 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>2.00pm</t>
+          <t>1.58pm</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>2.30pm</t>
+          <t>2.28pm</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -4639,12 +4639,12 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>2.30pm</t>
+          <t>2.28pm</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>3.00pm</t>
+          <t>2.58pm</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -4657,75 +4657,75 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>3.00pm</t>
+          <t>2.58pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
+          <t>3.58pm</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>3.58pm</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
           <t>4.00pm</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>4.00pm</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>5.30pm</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>BALINESE DANCE DEMONSTRATION</t>
         </is>
       </c>
-      <c r="D16" s="10" t="inlineStr">
+      <c r="D17" s="10" t="inlineStr">
         <is>
           <t>Performance · Indian Music Experience Museum, JP Nagar 7th Phase · 25 artists</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>5.30pm</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>5.50pm</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
+          <t>5.30pm</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
           <t>5.50pm</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>6.20pm</t>
-        </is>
-      </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr"/>
@@ -4733,20 +4733,38 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
+          <t>5.50pm</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
           <t>6.20pm</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>6.20pm</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>7.20pm</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C20" s="15" t="inlineStr">
         <is>
           <t>Dinner near Indian Music Experience Museum</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D20" s="18" t="inlineStr">
         <is>
           <t>added: the plan has dinner back at the stay</t>
         </is>
@@ -4855,7 +4873,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 02 · 51 km · live traffic · 10 min loading first</t>
+          <t>1 h 02 · 48 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5265,7 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>1 h 22 · 53 km · typical traffic for the day</t>
+          <t>1 h 22 · 53 km · traffic, refreshed hourly</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5472,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.24am</t>
+          <t>6.21am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5464,19 +5482,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>34 min · 25 km · live traffic · 10 min loading first</t>
+          <t>31 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.24am</t>
+          <t>6.21am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.34am</t>
+          <t>6.31am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5489,12 +5507,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.34am</t>
+          <t>6.31am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.49am</t>
+          <t>6.46am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5507,7 +5525,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.49am</t>
+          <t>6.46am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5707,7 +5725,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>3.12pm</t>
+          <t>3.13pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5717,19 +5735,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>27 min · 18 km · live traffic · 10 min loading first</t>
+          <t>28 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>3.12pm</t>
+          <t>3.13pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.43pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5742,12 +5760,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.43pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.12pm</t>
+          <t>4.13pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5760,12 +5778,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.12pm</t>
+          <t>4.13pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.12pm</t>
+          <t>5.13pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5778,7 +5796,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.12pm</t>
+          <t>5.13pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5948,7 +5966,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.19am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5958,19 +5976,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>38 min · 24 km · live traffic · 10 min loading first</t>
+          <t>39 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.19am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.28am</t>
+          <t>8.29am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -5983,12 +6001,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.28am</t>
+          <t>8.29am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.38am</t>
+          <t>8.39am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6001,12 +6019,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.38am</t>
+          <t>8.39am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>8.54am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6019,7 +6037,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>8.54am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -6122,7 +6140,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.32pm</t>
+          <t>1.33pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6132,19 +6150,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>42 min · 29 km · live traffic</t>
+          <t>43 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.32pm</t>
+          <t>1.33pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.02pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6157,12 +6175,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.02pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.32pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6175,7 +6193,7 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.32pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
@@ -6448,7 +6466,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6458,19 +6476,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic · 10 min loading first</t>
+          <t>40 min · 30 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6483,12 +6501,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.40pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6501,12 +6519,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.40pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.55pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6519,7 +6537,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.55pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6696,7 +6714,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6706,19 +6724,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic · 10 min loading first</t>
+          <t>40 min · 30 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6731,12 +6749,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.40pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6749,12 +6767,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.40pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.55pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6767,7 +6785,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.55pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>7.12am</t>
+          <t>7.27am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4.48pm</t>
+          <t>4.45pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1394,19 +1394,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>43 min · 27 km · live traffic · 10 min loading first</t>
+          <t>40 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>4.48pm</t>
+          <t>4.45pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>4.58pm</t>
+          <t>4.55pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>4.58pm</t>
+          <t>4.55pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1588,19 +1588,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>34 min · 22 km · live traffic · 10 min loading first</t>
+          <t>32 min · 22 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.22am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.22am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1631,12 +1631,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.47am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1649,7 +1649,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.47am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>2.48pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1761,7 +1761,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>2.48pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>12 min · 5 km · live traffic</t>
+          <t>11 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>3.49pm</t>
+          <t>3.48pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>34 min · 22 km · live traffic · 10 min loading first</t>
+          <t>33 min · 21 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.49pm</t>
+          <t>3.48pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.19pm</t>
+          <t>4.18pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3104,12 +3104,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.19pm</t>
+          <t>4.18pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>4.49pm</t>
+          <t>4.48pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3122,12 +3122,12 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>4.49pm</t>
+          <t>4.48pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>5.49pm</t>
+          <t>5.48pm</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -3140,7 +3140,7 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>5.49pm</t>
+          <t>5.48pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -3328,19 +3328,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>37 min · 25 km · live traffic · 10 min loading first</t>
+          <t>36 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3353,12 +3353,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.37am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.37am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.52am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3389,7 +3389,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.52am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -3739,19 +3739,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>37 min · 25 km · live traffic · 10 min loading first</t>
+          <t>36 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -3764,12 +3764,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.37am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3782,12 +3782,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.37am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.52am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3800,7 +3800,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.52am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -3903,7 +3903,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>4.40pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>5.22pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -3949,19 +3949,19 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>40 min · 26 km · live traffic · 10 min loading first</t>
+          <t>39 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>5.22pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>5.52pm</t>
+          <t>5.51pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3974,12 +3974,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>5.52pm</t>
+          <t>5.51pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>6.22pm</t>
+          <t>6.21pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -3992,12 +3992,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>6.22pm</t>
+          <t>6.21pm</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>7.22pm</t>
+          <t>7.21pm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -4010,7 +4010,7 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>7.22pm</t>
+          <t>7.21pm</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 27 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 42 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>7.12am</t>
+          <t>7.27am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4222,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 27 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 42 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>7.12am</t>
+          <t>7.27am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.42am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.42am</t>
+          <t>8.57am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.12am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.12am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.42am</t>
+          <t>9.57am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.42am</t>
+          <t>9.57am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>6 h 57 · 387 km · live traffic · home about 5.32am (+1)</t>
+          <t>6 h 46 · 387 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>1.58pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -4614,19 +4614,19 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>43 min · 27 km · live traffic · 10 min loading first</t>
+          <t>40 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>1.58pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.25pm</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -4639,12 +4639,12 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.25pm</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>2.55pm</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -4657,12 +4657,12 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>2.58pm</t>
+          <t>2.55pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>3.58pm</t>
+          <t>3.55pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -4675,7 +4675,7 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>3.58pm</t>
+          <t>3.55pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4873,19 +4873,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 02 · 48 km · live traffic · 10 min loading first</t>
+          <t>1 h 03 · 48 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.57pm</t>
+          <t>6.58pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>3.13pm</t>
+          <t>3.12pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5735,19 +5735,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>28 min · 18 km · live traffic · 10 min loading first</t>
+          <t>27 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>3.13pm</t>
+          <t>3.12pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.43pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5760,12 +5760,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.43pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.13pm</t>
+          <t>4.12pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5778,12 +5778,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.13pm</t>
+          <t>4.12pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.13pm</t>
+          <t>5.12pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5796,7 +5796,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.13pm</t>
+          <t>5.12pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5906,7 +5906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>8.19am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5976,19 +5976,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>39 min · 24 km · live traffic · 10 min loading first</t>
+          <t>37 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>8.19am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.29am</t>
+          <t>8.27am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -6001,12 +6001,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.29am</t>
+          <t>8.27am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.39am</t>
+          <t>8.37am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6019,12 +6019,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.39am</t>
+          <t>8.37am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.54am</t>
+          <t>8.52am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6037,7 +6037,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.54am</t>
+          <t>8.52am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.28pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6150,19 +6150,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>43 min · 26 km · live traffic</t>
+          <t>38 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.28pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>1.58pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6175,12 +6175,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>1.58pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.28pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6193,97 +6193,97 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.28pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
+          <t>3.28pm</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>3.28pm</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>3.30pm</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
+          <t>3.30pm</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
@@ -6291,20 +6291,38 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>10.50pm</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr"/>
+      <c r="D24" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6466,7 +6484,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6476,19 +6494,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>40 min · 30 km · live traffic · 10 min loading first</t>
+          <t>39 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6501,12 +6519,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6519,12 +6537,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.55pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6537,7 +6555,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.55pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6714,7 +6732,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6724,19 +6742,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>40 min · 30 km · live traffic · 10 min loading first</t>
+          <t>39 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6749,12 +6767,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6767,12 +6785,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.55pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6785,7 +6803,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.55pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>7.27am</t>
+          <t>6.53am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1761,7 +1761,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>11 min · 5 km · live traffic</t>
+          <t>10 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>3.48pm</t>
+          <t>3.47pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>33 min · 21 km · live traffic · 10 min loading first</t>
+          <t>32 min · 21 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.48pm</t>
+          <t>3.47pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.18pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3104,12 +3104,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.18pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>4.48pm</t>
+          <t>4.47pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3122,12 +3122,12 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>4.48pm</t>
+          <t>4.47pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>5.48pm</t>
+          <t>5.47pm</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -3140,7 +3140,7 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>5.48pm</t>
+          <t>5.47pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -3328,19 +3328,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>36 min · 25 km · live traffic · 10 min loading first</t>
+          <t>35 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3353,12 +3353,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3389,7 +3389,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -3739,19 +3739,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>36 min · 25 km · live traffic · 10 min loading first</t>
+          <t>35 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>9.16am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -3764,12 +3764,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.26am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3782,12 +3782,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3800,7 +3800,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>1.53pm</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>35 min · 24 km · live traffic</t>
+          <t>33 min · 24 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>1.53pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
@@ -3916,12 +3916,12 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>1.53pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.55pm</t>
+          <t>2.53pm</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 42 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 08 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>7.27am</t>
+          <t>6.53am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4222,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 42 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 08 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>7.27am</t>
+          <t>6.53am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.23am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.57am</t>
+          <t>8.23am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.57am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.57am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>6 h 46 · 387 km · live traffic · home about 5.32am (+1)</t>
+          <t>6 h 40 · 387 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.26pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4873,19 +4873,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 03 · 48 km · live traffic · 10 min loading first</t>
+          <t>1 h 01 · 48 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.26pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.58pm</t>
+          <t>6.56pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>9.36pm</t>
+          <t>9.13pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5265,14 +5265,14 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>1 h 22 · 53 km · traffic, refreshed hourly</t>
+          <t>59 min · 48 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.36pm</t>
+          <t>9.13pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>3.12pm</t>
+          <t>3.11pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5735,19 +5735,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>27 min · 18 km · live traffic · 10 min loading first</t>
+          <t>26 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>3.12pm</t>
+          <t>3.11pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.41pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5760,12 +5760,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.41pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.12pm</t>
+          <t>4.11pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5778,12 +5778,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.12pm</t>
+          <t>4.11pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.12pm</t>
+          <t>5.11pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5796,7 +5796,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.12pm</t>
+          <t>5.11pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5906,7 +5906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.16am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5976,19 +5976,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>37 min · 24 km · live traffic · 10 min loading first</t>
+          <t>36 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.16am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.27am</t>
+          <t>8.26am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -6001,12 +6001,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.27am</t>
+          <t>8.26am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.37am</t>
+          <t>8.36am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6019,12 +6019,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.37am</t>
+          <t>8.36am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.52am</t>
+          <t>8.51am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6037,7 +6037,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.52am</t>
+          <t>8.51am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.28pm</t>
+          <t>1.31pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6150,19 +6150,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic</t>
+          <t>41 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.28pm</t>
+          <t>1.31pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>1.58pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6175,12 +6175,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>1.58pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6193,12 +6193,12 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -6208,38 +6208,42 @@
       </c>
       <c r="D18" s="7" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>3.28pm</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr"/>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -6248,42 +6252,38 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
@@ -6291,38 +6291,20 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>6.53am</t>
+          <t>7.21am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2236,19 +2236,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>31 min · 25 km · live traffic · 10 min loading first</t>
+          <t>29 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2261,12 +2261,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2279,12 +2279,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.46am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2297,7 +2297,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.46am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2654,19 +2654,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>31 min · 25 km · live traffic · 10 min loading first</t>
+          <t>29 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2679,12 +2679,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.46am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2715,7 +2715,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.46am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>32 min · 21 km · live traffic · 10 min loading first</t>
+          <t>32 min · 22 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>35 min · 24 km · live traffic · 10 min loading first</t>
+          <t>35 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>35 min · 24 km · live traffic · 10 min loading first</t>
+          <t>35 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>4.41pm</t>
+          <t>4.42pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -3949,19 +3949,19 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic · 10 min loading first</t>
+          <t>38 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>5.51pm</t>
+          <t>5.50pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3974,12 +3974,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>5.51pm</t>
+          <t>5.50pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>6.21pm</t>
+          <t>6.20pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -3992,12 +3992,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>6.21pm</t>
+          <t>6.20pm</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>7.21pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -4010,7 +4010,7 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>7.21pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 08 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 36 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>6.53am</t>
+          <t>7.21am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4222,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 08 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 36 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>6.53am</t>
+          <t>7.21am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.23am</t>
+          <t>8.51am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.23am</t>
+          <t>8.51am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>6 h 40 · 387 km · live traffic · home about 5.32am (+1)</t>
+          <t>6 h 45 · 387 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>9.13pm</t>
+          <t>9.12pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5265,14 +5265,14 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>59 min · 48 km · live traffic</t>
+          <t>58 min · 48 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.13pm</t>
+          <t>9.12pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.21am</t>
+          <t>6.19am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5482,19 +5482,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>31 min · 25 km · live traffic · 10 min loading first</t>
+          <t>29 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.21am</t>
+          <t>6.19am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.31am</t>
+          <t>6.29am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5507,12 +5507,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.31am</t>
+          <t>6.29am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.46am</t>
+          <t>6.44am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5525,7 +5525,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.46am</t>
+          <t>6.44am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5906,7 +5906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.25pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6150,19 +6150,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>41 min · 29 km · live traffic</t>
+          <t>35 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.25pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6175,12 +6175,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.25pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6193,97 +6193,97 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.25pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
+          <t>3.25pm</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>3.25pm</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>3.30pm</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
+          <t>3.30pm</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
@@ -6291,20 +6291,38 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>10.50pm</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr"/>
+      <c r="D24" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6466,7 +6484,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6476,19 +6494,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic · 10 min loading first</t>
+          <t>37 min · 30 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6501,12 +6519,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.37pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6519,12 +6537,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.37pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.52pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6537,7 +6555,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.52pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6714,7 +6732,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6724,19 +6742,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic · 10 min loading first</t>
+          <t>37 min · 30 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6749,12 +6767,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.37pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6767,12 +6785,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.37pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.52pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6785,7 +6803,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.52pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>7.21am</t>
+          <t>7.11am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1761,7 +1761,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>2.50pm</t>
+          <t>2.49pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>10 min · 5 km · live traffic</t>
+          <t>11 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2236,19 +2236,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>29 min · 25 km · live traffic · 10 min loading first</t>
+          <t>31 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2261,12 +2261,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2279,12 +2279,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.46am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2297,7 +2297,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.46am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2654,19 +2654,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>29 min · 25 km · live traffic · 10 min loading first</t>
+          <t>31 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2679,12 +2679,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.21am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.31am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.46am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2715,7 +2715,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.46am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>3.47pm</t>
+          <t>3.48pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>32 min · 22 km · live traffic · 10 min loading first</t>
+          <t>33 min · 22 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.47pm</t>
+          <t>3.48pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.18pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3104,12 +3104,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.18pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>4.47pm</t>
+          <t>4.48pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3122,12 +3122,12 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>4.47pm</t>
+          <t>4.48pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>5.47pm</t>
+          <t>5.48pm</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -3140,7 +3140,7 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>5.47pm</t>
+          <t>5.48pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>35 min · 25 km · live traffic · 10 min loading first</t>
+          <t>35 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>35 min · 25 km · live traffic · 10 min loading first</t>
+          <t>35 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>4.42pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -3949,19 +3949,19 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic · 10 min loading first</t>
+          <t>39 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>5.50pm</t>
+          <t>5.51pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3974,12 +3974,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>5.50pm</t>
+          <t>5.51pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>6.20pm</t>
+          <t>6.21pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -3992,12 +3992,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>6.20pm</t>
+          <t>6.21pm</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>7.20pm</t>
+          <t>7.21pm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -4010,7 +4010,7 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>7.20pm</t>
+          <t>7.21pm</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 36 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 26 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>7.21am</t>
+          <t>7.11am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4222,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 36 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 26 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>7.21am</t>
+          <t>7.11am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.51am</t>
+          <t>8.41am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.51am</t>
+          <t>8.41am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.41am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.51am</t>
+          <t>9.41am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>6 h 45 · 387 km · live traffic · home about 5.32am (+1)</t>
+          <t>6 h 58 · 397 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>9.12pm</t>
+          <t>9.13pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5265,14 +5265,14 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>58 min · 48 km · live traffic</t>
+          <t>59 min · 48 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.12pm</t>
+          <t>9.13pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.19am</t>
+          <t>6.21am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5482,19 +5482,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>29 min · 25 km · live traffic · 10 min loading first</t>
+          <t>31 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.19am</t>
+          <t>6.21am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.29am</t>
+          <t>6.31am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5507,12 +5507,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.29am</t>
+          <t>6.31am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.44am</t>
+          <t>6.46am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5525,7 +5525,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.44am</t>
+          <t>6.46am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5906,7 +5906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>8.16am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5976,19 +5976,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>36 min · 24 km · live traffic · 10 min loading first</t>
+          <t>37 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>8.16am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.26am</t>
+          <t>8.27am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -6001,12 +6001,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.26am</t>
+          <t>8.27am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.36am</t>
+          <t>8.37am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6019,12 +6019,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.36am</t>
+          <t>8.37am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.51am</t>
+          <t>8.52am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6037,7 +6037,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.51am</t>
+          <t>8.52am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.25pm</t>
+          <t>1.31pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6150,19 +6150,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>35 min · 26 km · live traffic</t>
+          <t>41 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.25pm</t>
+          <t>1.31pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6175,12 +6175,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.25pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6193,12 +6193,12 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.25pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>3.25pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -6208,38 +6208,42 @@
       </c>
       <c r="D18" s="7" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>3.25pm</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr"/>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -6248,42 +6252,38 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
@@ -6291,38 +6291,20 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6484,7 +6466,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6494,19 +6476,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>37 min · 30 km · live traffic · 10 min loading first</t>
+          <t>39 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6519,12 +6501,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.37pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6537,12 +6519,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.37pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.52pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6555,7 +6537,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.52pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6732,7 +6714,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6742,19 +6724,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>37 min · 30 km · live traffic · 10 min loading first</t>
+          <t>39 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6767,12 +6749,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.37pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6785,12 +6767,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.37pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.52pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6803,7 +6785,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.52pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>7.11am</t>
+          <t>7.06am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1761,7 +1761,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>2.49pm</t>
+          <t>2.50pm</t>
         </is>
       </c>
       <c r="B17" s="11" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>11 min · 5 km · live traffic</t>
+          <t>10 min · 5 km · live traffic</t>
         </is>
       </c>
     </row>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2236,19 +2236,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>31 min · 25 km · live traffic · 10 min loading first</t>
+          <t>33 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2261,12 +2261,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2279,12 +2279,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.46am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2297,7 +2297,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.46am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2654,19 +2654,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>31 min · 25 km · live traffic · 10 min loading first</t>
+          <t>33 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2679,12 +2679,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.21am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.31am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.46am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2715,7 +2715,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.46am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>3.48pm</t>
+          <t>3.47pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>33 min · 22 km · live traffic · 10 min loading first</t>
+          <t>32 min · 21 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.48pm</t>
+          <t>3.47pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.18pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3104,12 +3104,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.18pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>4.48pm</t>
+          <t>4.47pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3122,12 +3122,12 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>4.48pm</t>
+          <t>4.47pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>5.48pm</t>
+          <t>5.47pm</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -3140,7 +3140,7 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>5.48pm</t>
+          <t>5.47pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>35 min · 24 km · live traffic · 10 min loading first</t>
+          <t>35 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>35 min · 24 km · live traffic · 10 min loading first</t>
+          <t>35 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>4.41pm</t>
+          <t>4.42pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -3949,19 +3949,19 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic · 10 min loading first</t>
+          <t>38 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>5.21pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>5.51pm</t>
+          <t>5.50pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3974,12 +3974,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>5.51pm</t>
+          <t>5.50pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>6.21pm</t>
+          <t>6.20pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -3992,12 +3992,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>6.21pm</t>
+          <t>6.20pm</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>7.21pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -4010,7 +4010,7 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>7.21pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 26 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 21 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>7.11am</t>
+          <t>7.06am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4222,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 26 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 21 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>7.11am</t>
+          <t>7.06am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.41am</t>
+          <t>8.36am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.41am</t>
+          <t>8.36am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>6 h 58 · 397 km · live traffic · home about 5.32am (+1)</t>
+          <t>7 h 01 · 397 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>9.13pm</t>
+          <t>9.12pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5265,14 +5265,14 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>59 min · 48 km · live traffic</t>
+          <t>58 min · 48 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.13pm</t>
+          <t>9.12pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.21am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5482,19 +5482,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>31 min · 25 km · live traffic · 10 min loading first</t>
+          <t>33 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.21am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.31am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5507,12 +5507,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.31am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.46am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5525,7 +5525,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.46am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.30pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6150,19 +6150,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>41 min · 26 km · live traffic</t>
+          <t>40 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.30pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>2.00pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6175,12 +6175,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>2.00pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.30pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6193,7 +6193,7 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.30pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6476,19 +6476,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic · 10 min loading first</t>
+          <t>38 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6501,12 +6501,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.38pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6519,12 +6519,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.38pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.53pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6537,7 +6537,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.53pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6724,19 +6724,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic · 10 min loading first</t>
+          <t>38 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.18pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6749,12 +6749,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.38pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6767,12 +6767,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.38pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.53pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6785,7 +6785,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.53pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>7.06am</t>
+          <t>7.00am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 21 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 15 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>7.06am</t>
+          <t>7.00am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4222,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 21 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 15 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>7.06am</t>
+          <t>7.00am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.36am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.36am</t>
+          <t>8.30am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.00am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.00am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.30am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.30am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>7 h 01 · 397 km · live traffic · home about 5.32am (+1)</t>
+          <t>7 h 04 · 397 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.30pm</t>
+          <t>1.28pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6150,19 +6150,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>40 min · 26 km · live traffic</t>
+          <t>38 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.30pm</t>
+          <t>1.28pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.00pm</t>
+          <t>1.58pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6175,12 +6175,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.00pm</t>
+          <t>1.58pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.30pm</t>
+          <t>2.28pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6193,97 +6193,97 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.30pm</t>
+          <t>2.28pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
+          <t>3.28pm</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>3.28pm</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>3.30pm</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
+          <t>3.30pm</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
@@ -6291,20 +6291,38 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>10.50pm</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr"/>
+      <c r="D24" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6466,7 +6484,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6476,19 +6494,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic · 10 min loading first</t>
+          <t>39 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6501,12 +6519,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.38pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6519,12 +6537,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.38pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.53pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6537,7 +6555,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.53pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6714,7 +6732,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6724,19 +6742,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic · 10 min loading first</t>
+          <t>39 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.18pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6749,12 +6767,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.38pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6767,12 +6785,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.38pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.53pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6785,7 +6803,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.53pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>7.00am</t>
+          <t>7.06am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4.45pm</t>
+          <t>4.47pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1394,19 +1394,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>40 min · 27 km · live traffic · 10 min loading first</t>
+          <t>42 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>4.45pm</t>
+          <t>4.47pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>4.55pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>4.55pm</t>
+          <t>4.57pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.12am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1588,19 +1588,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>32 min · 22 km · live traffic · 10 min loading first</t>
+          <t>34 min · 22 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.12am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.22am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.22am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1631,12 +1631,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.47am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1649,7 +1649,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.47am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2236,19 +2236,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>33 min · 25 km · live traffic · 10 min loading first</t>
+          <t>32 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.22am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2261,12 +2261,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.22am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2279,12 +2279,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.47am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2297,7 +2297,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.47am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2654,19 +2654,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>33 min · 25 km · live traffic · 10 min loading first</t>
+          <t>32 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.22am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2679,12 +2679,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.22am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.47am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2715,7 +2715,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.47am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>3.47pm</t>
+          <t>3.49pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>32 min · 21 km · live traffic · 10 min loading first</t>
+          <t>34 min · 22 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.47pm</t>
+          <t>3.49pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.19pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3104,12 +3104,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.19pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>4.47pm</t>
+          <t>4.49pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3122,12 +3122,12 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>4.47pm</t>
+          <t>4.49pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>5.47pm</t>
+          <t>5.49pm</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -3140,7 +3140,7 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>5.47pm</t>
+          <t>5.49pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -3328,19 +3328,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>35 min · 25 km · live traffic · 10 min loading first</t>
+          <t>37 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3353,12 +3353,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.37am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.37am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.52am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3389,7 +3389,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.52am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -3739,19 +3739,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>35 min · 25 km · live traffic · 10 min loading first</t>
+          <t>37 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.17am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -3764,12 +3764,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.27am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.37am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3782,12 +3782,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.37am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.52am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3800,7 +3800,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.52am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>1.53pm</t>
+          <t>1.56pm</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -3891,19 +3891,19 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>33 min · 24 km · live traffic</t>
+          <t>36 min · 24 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>1.53pm</t>
+          <t>1.56pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>4.42pm</t>
+          <t>4.40pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -3916,12 +3916,12 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.53pm</t>
+          <t>1.56pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.53pm</t>
+          <t>2.56pm</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.22pm</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -3949,19 +3949,19 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic · 10 min loading first</t>
+          <t>40 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.22pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>5.50pm</t>
+          <t>5.52pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3974,12 +3974,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>5.50pm</t>
+          <t>5.52pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>6.20pm</t>
+          <t>6.22pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -3992,12 +3992,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>6.20pm</t>
+          <t>6.22pm</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>7.20pm</t>
+          <t>7.22pm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -4010,7 +4010,7 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>7.20pm</t>
+          <t>7.22pm</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 15 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 21 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>7.00am</t>
+          <t>7.06am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4222,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 15 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 21 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>7.00am</t>
+          <t>7.06am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.30am</t>
+          <t>8.36am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.30am</t>
+          <t>8.36am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.00am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.00am</t>
+          <t>9.06am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.30am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.30am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>7 h 04 · 397 km · live traffic · home about 5.32am (+1)</t>
+          <t>6 h 53 · 397 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>1.57pm</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -4614,19 +4614,19 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>40 min · 27 km · live traffic · 10 min loading first</t>
+          <t>42 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>1.57pm</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>2.25pm</t>
+          <t>2.27pm</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -4639,12 +4639,12 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>2.25pm</t>
+          <t>2.27pm</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>2.55pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -4657,12 +4657,12 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>2.55pm</t>
+          <t>2.57pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>3.55pm</t>
+          <t>3.57pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -4675,7 +4675,7 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>3.55pm</t>
+          <t>3.57pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.26pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4873,19 +4873,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 01 · 48 km · live traffic · 10 min loading first</t>
+          <t>1 h 04 · 48 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.26pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.56pm</t>
+          <t>6.59pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>9.12pm</t>
+          <t>9.14pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5265,14 +5265,14 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>58 min · 48 km · live traffic</t>
+          <t>1 h · 48 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.12pm</t>
+          <t>9.14pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.22am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5482,19 +5482,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>33 min · 25 km · live traffic · 10 min loading first</t>
+          <t>32 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.22am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.32am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5507,12 +5507,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.32am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.47am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5525,7 +5525,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.47am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>3.11pm</t>
+          <t>3.13pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5735,19 +5735,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>26 min · 18 km · live traffic · 10 min loading first</t>
+          <t>28 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>3.11pm</t>
+          <t>3.13pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.41pm</t>
+          <t>3.43pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5760,12 +5760,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.41pm</t>
+          <t>3.43pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.11pm</t>
+          <t>4.13pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5778,12 +5778,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.11pm</t>
+          <t>4.13pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.11pm</t>
+          <t>5.13pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5796,7 +5796,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.11pm</t>
+          <t>5.13pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5906,7 +5906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5976,19 +5976,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>37 min · 24 km · live traffic · 10 min loading first</t>
+          <t>38 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.27am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -6001,12 +6001,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.27am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.37am</t>
+          <t>8.38am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6019,12 +6019,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.37am</t>
+          <t>8.38am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.52am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6037,7 +6037,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.52am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.28pm</t>
+          <t>1.32pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6150,19 +6150,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic</t>
+          <t>42 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.28pm</t>
+          <t>1.32pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>1.58pm</t>
+          <t>2.02pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6175,12 +6175,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>1.58pm</t>
+          <t>2.02pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.32pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6193,12 +6193,12 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.28pm</t>
+          <t>2.32pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>3.28pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -6208,38 +6208,42 @@
       </c>
       <c r="D18" s="7" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>3.28pm</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr"/>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -6248,42 +6252,38 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
@@ -6291,38 +6291,20 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6484,7 +6466,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6494,19 +6476,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic · 10 min loading first</t>
+          <t>40 min · 30 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6519,12 +6501,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.40pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6537,12 +6519,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.40pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.55pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6555,7 +6537,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.55pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6732,7 +6714,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6742,19 +6724,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>39 min · 26 km · live traffic · 10 min loading first</t>
+          <t>40 min · 30 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.19pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6767,12 +6749,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.40pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6785,12 +6767,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.39pm</t>
+          <t>5.40pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.55pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6803,7 +6785,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.54pm</t>
+          <t>5.55pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>7.06am</t>
+          <t>7.23am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4.47pm</t>
+          <t>4.45pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1394,19 +1394,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>42 min · 27 km · live traffic · 10 min loading first</t>
+          <t>40 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>4.47pm</t>
+          <t>4.45pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>4.57pm</t>
+          <t>4.55pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>4.57pm</t>
+          <t>4.55pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1588,19 +1588,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>34 min · 22 km · live traffic · 10 min loading first</t>
+          <t>32 min · 22 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.12am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.22am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1613,12 +1613,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.24am</t>
+          <t>9.22am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -1631,12 +1631,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.34am</t>
+          <t>9.32am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.47am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -1649,7 +1649,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.49am</t>
+          <t>9.47am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.12am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2236,19 +2236,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>32 min · 25 km · live traffic · 10 min loading first</t>
+          <t>29 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.12am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.22am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2261,12 +2261,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.22am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2279,12 +2279,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.47am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2297,7 +2297,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.47am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.12am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2654,19 +2654,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>32 min · 25 km · live traffic · 10 min loading first</t>
+          <t>29 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.12am</t>
+          <t>9.09am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.22am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2679,12 +2679,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.22am</t>
+          <t>9.19am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.32am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.47am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2715,7 +2715,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.47am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>3.49pm</t>
+          <t>3.47pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>34 min · 22 km · live traffic · 10 min loading first</t>
+          <t>32 min · 21 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.49pm</t>
+          <t>3.47pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.19pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3104,12 +3104,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.19pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>4.49pm</t>
+          <t>4.47pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3122,12 +3122,12 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>4.49pm</t>
+          <t>4.47pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>5.49pm</t>
+          <t>5.47pm</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -3140,7 +3140,7 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>5.49pm</t>
+          <t>5.47pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -3328,19 +3328,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>37 min · 25 km · live traffic · 10 min loading first</t>
+          <t>35 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3353,12 +3353,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.37am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.37am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.52am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3389,7 +3389,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.52am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -3739,19 +3739,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>37 min · 25 km · live traffic · 10 min loading first</t>
+          <t>35 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>9.17am</t>
+          <t>9.15am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -3764,12 +3764,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.27am</t>
+          <t>9.25am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.37am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3782,12 +3782,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.37am</t>
+          <t>9.35am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.52am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3800,7 +3800,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.52am</t>
+          <t>9.50am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>1.56pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -3891,19 +3891,19 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>36 min · 24 km · live traffic</t>
+          <t>35 min · 24 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>1.56pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>4.40pm</t>
+          <t>4.42pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -3916,12 +3916,12 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.56pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.56pm</t>
+          <t>2.55pm</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>5.22pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -3949,19 +3949,19 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>40 min · 26 km · live traffic · 10 min loading first</t>
+          <t>38 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>5.22pm</t>
+          <t>5.20pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>5.52pm</t>
+          <t>5.50pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3974,12 +3974,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>5.52pm</t>
+          <t>5.50pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>6.22pm</t>
+          <t>6.20pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -3992,12 +3992,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>6.22pm</t>
+          <t>6.20pm</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>7.22pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -4010,7 +4010,7 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>7.22pm</t>
+          <t>7.20pm</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 21 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 38 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>7.06am</t>
+          <t>7.23am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4222,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 21 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 38 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>7.06am</t>
+          <t>7.23am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.36am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.36am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.06am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.53am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.36am</t>
+          <t>9.53am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>6 h 53 · 397 km · live traffic · home about 5.32am (+1)</t>
+          <t>6 h 42 · 387 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>1.57pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -4614,19 +4614,19 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>42 min · 27 km · live traffic · 10 min loading first</t>
+          <t>40 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>1.57pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>2.27pm</t>
+          <t>2.25pm</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -4639,12 +4639,12 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>2.27pm</t>
+          <t>2.25pm</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>2.55pm</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -4657,12 +4657,12 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>2.57pm</t>
+          <t>2.55pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>3.57pm</t>
+          <t>3.55pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -4675,7 +4675,7 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>3.57pm</t>
+          <t>3.55pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.26pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4873,19 +4873,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 04 · 48 km · live traffic · 10 min loading first</t>
+          <t>1 h 01 · 51 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.29pm</t>
+          <t>5.26pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.59pm</t>
+          <t>6.56pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>9.14pm</t>
+          <t>9.11pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5265,14 +5265,14 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>1 h · 48 km · live traffic</t>
+          <t>57 min · 48 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.14pm</t>
+          <t>9.11pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.22am</t>
+          <t>6.19am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5482,19 +5482,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>32 min · 25 km · live traffic · 10 min loading first</t>
+          <t>29 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.22am</t>
+          <t>6.19am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.32am</t>
+          <t>6.29am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5507,12 +5507,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.32am</t>
+          <t>6.29am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.47am</t>
+          <t>6.44am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5525,7 +5525,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.47am</t>
+          <t>6.44am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>3.13pm</t>
+          <t>3.11pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5735,19 +5735,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>28 min · 18 km · live traffic · 10 min loading first</t>
+          <t>26 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>3.13pm</t>
+          <t>3.11pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.43pm</t>
+          <t>3.41pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5760,12 +5760,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.43pm</t>
+          <t>3.41pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.13pm</t>
+          <t>4.11pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5778,12 +5778,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.13pm</t>
+          <t>4.11pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.13pm</t>
+          <t>5.11pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5796,7 +5796,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.13pm</t>
+          <t>5.11pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5906,7 +5906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.16am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5976,19 +5976,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>38 min · 24 km · live traffic · 10 min loading first</t>
+          <t>36 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.16am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.28am</t>
+          <t>8.26am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -6001,12 +6001,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.28am</t>
+          <t>8.26am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.38am</t>
+          <t>8.36am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6019,12 +6019,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.38am</t>
+          <t>8.36am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>8.51am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6037,7 +6037,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>8.51am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.32pm</t>
+          <t>1.24pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6150,19 +6150,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>42 min · 26 km · live traffic</t>
+          <t>34 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.32pm</t>
+          <t>1.24pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.02pm</t>
+          <t>1.54pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6175,12 +6175,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.02pm</t>
+          <t>1.54pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.32pm</t>
+          <t>2.24pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6193,97 +6193,97 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.32pm</t>
+          <t>2.24pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
+          <t>3.24pm</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Costume, make-up, warm-up &amp; call</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
+          <t>3.24pm</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Costume, make-up, warm-up &amp; call</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>3.30pm</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>5.00pm</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
-        </is>
-      </c>
-      <c r="D19" s="10" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Spare time at the venue</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
+          <t>3.30pm</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
           <t>7.30pm</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
         <is>
           <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
-      <c r="D20" s="10" t="inlineStr">
+      <c r="D21" s="10" t="inlineStr">
         <is>
           <t>Performance · Jagriti Theatre, Whitefield</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="inlineStr">
-        <is>
-          <t>9.00pm</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>9.20pm</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Costume off, make-up removal &amp; change</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
+          <t>9.00pm</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
           <t>9.20pm</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>Costume off, make-up removal &amp; change</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
@@ -6291,20 +6291,38 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
           <t>9.50pm</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Wrap — pack, meet people, load-out</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>9.50pm</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
         <is>
           <t>10.50pm</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C24" s="15" t="inlineStr">
         <is>
           <t>Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr"/>
+      <c r="D24" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6466,7 +6484,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6476,19 +6494,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>40 min · 30 km · live traffic · 10 min loading first</t>
+          <t>37 min · 30 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6501,12 +6519,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>5.37pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6519,12 +6537,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>5.37pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.55pm</t>
+          <t>5.52pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6537,7 +6555,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.55pm</t>
+          <t>5.52pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6714,7 +6732,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6724,19 +6742,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>40 min · 30 km · live traffic · 10 min loading first</t>
+          <t>37 min · 30 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.17pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6749,12 +6767,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>5.37pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6767,12 +6785,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.40pm</t>
+          <t>5.37pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.55pm</t>
+          <t>5.52pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6785,7 +6803,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.55pm</t>
+          <t>5.52pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>7.23am</t>
+          <t>7.11am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2236,19 +2236,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>29 min · 25 km · live traffic · 10 min loading first</t>
+          <t>33 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2261,12 +2261,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2279,12 +2279,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2297,7 +2297,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2654,19 +2654,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>29 min · 25 km · live traffic · 10 min loading first</t>
+          <t>33 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.09am</t>
+          <t>9.13am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2679,12 +2679,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.19am</t>
+          <t>9.23am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.29am</t>
+          <t>9.33am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2715,7 +2715,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.48am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>3.47pm</t>
+          <t>3.48pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>32 min · 21 km · live traffic · 10 min loading first</t>
+          <t>33 min · 21 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.47pm</t>
+          <t>3.48pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.18pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3104,12 +3104,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.18pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>4.47pm</t>
+          <t>4.48pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3122,12 +3122,12 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>4.47pm</t>
+          <t>4.48pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>5.47pm</t>
+          <t>5.48pm</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -3140,7 +3140,7 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>5.47pm</t>
+          <t>5.48pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>35 min · 25 km · live traffic · 10 min loading first</t>
+          <t>35 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>35 min · 25 km · live traffic · 10 min loading first</t>
+          <t>35 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>1.54pm</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -3891,19 +3891,19 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>35 min · 24 km · live traffic</t>
+          <t>34 min · 24 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>1.54pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>4.42pm</t>
+          <t>4.41pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -3916,12 +3916,12 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>1.54pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.55pm</t>
+          <t>2.54pm</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -3949,19 +3949,19 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>38 min · 26 km · live traffic · 10 min loading first</t>
+          <t>39 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>5.20pm</t>
+          <t>5.21pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>5.50pm</t>
+          <t>5.51pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -3974,12 +3974,12 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
-          <t>5.50pm</t>
+          <t>5.51pm</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>6.20pm</t>
+          <t>6.21pm</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -3992,12 +3992,12 @@
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
         <is>
-          <t>6.20pm</t>
+          <t>6.21pm</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>7.20pm</t>
+          <t>7.21pm</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -4010,7 +4010,7 @@
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>7.20pm</t>
+          <t>7.21pm</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 38 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 26 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>7.23am</t>
+          <t>7.11am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4222,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 38 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 26 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>7.23am</t>
+          <t>7.11am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>8.41am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>8.41am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.11am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.53am</t>
+          <t>9.41am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.53am</t>
+          <t>9.41am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>6 h 42 · 387 km · live traffic · home about 5.32am (+1)</t>
+          <t>6 h 45 · 387 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.26pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4873,19 +4873,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 01 · 51 km · live traffic · 10 min loading first</t>
+          <t>1 h 05 · 48 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.26pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.56pm</t>
+          <t>7.00pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>9.11pm</t>
+          <t>9.14pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5265,14 +5265,14 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>57 min · 48 km · live traffic</t>
+          <t>1 h · 48 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.11pm</t>
+          <t>9.14pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.19am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5482,19 +5482,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>29 min · 25 km · live traffic · 10 min loading first</t>
+          <t>33 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.19am</t>
+          <t>6.23am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.29am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5507,12 +5507,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.29am</t>
+          <t>6.33am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.44am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5525,7 +5525,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.44am</t>
+          <t>6.48am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>3.11pm</t>
+          <t>3.12pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5735,19 +5735,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>26 min · 18 km · live traffic · 10 min loading first</t>
+          <t>27 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>3.11pm</t>
+          <t>3.12pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.41pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5760,12 +5760,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.41pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.11pm</t>
+          <t>4.12pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5778,12 +5778,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.11pm</t>
+          <t>4.12pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.11pm</t>
+          <t>5.12pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5796,7 +5796,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.11pm</t>
+          <t>5.12pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5906,7 +5906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5966,7 +5966,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>8.16am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5976,19 +5976,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>36 min · 24 km · live traffic · 10 min loading first</t>
+          <t>38 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>8.16am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.26am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -6001,12 +6001,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.26am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.36am</t>
+          <t>8.38am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6019,12 +6019,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.36am</t>
+          <t>8.38am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.51am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6037,7 +6037,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.51am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.24pm</t>
+          <t>1.33pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6150,19 +6150,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>34 min · 26 km · live traffic</t>
+          <t>43 min · 26 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.24pm</t>
+          <t>1.33pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>1.54pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6175,12 +6175,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>1.54pm</t>
+          <t>2.03pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.24pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6193,12 +6193,12 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.24pm</t>
+          <t>2.33pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>3.24pm</t>
+          <t>3.30pm</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -6208,38 +6208,42 @@
       </c>
       <c r="D18" s="7" t="inlineStr"/>
     </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>3.24pm</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>3.30pm</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Spare time at the venue</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr"/>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>5.00pm</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Performance · Jagriti Theatre, Whitefield</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>3.30pm</t>
+          <t>7.30pm</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>5.00pm</t>
+          <t>9.00pm</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 1</t>
+          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
@@ -6248,42 +6252,38 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>7.30pm</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>9.00pm</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>SHADOW PUPPETRY PERFORMANCE — SHOW 2</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Performance · Jagriti Theatre, Whitefield</t>
-        </is>
-      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>9.20pm</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Costume off, make-up removal &amp; change</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
         <is>
-          <t>9.00pm</t>
+          <t>9.20pm</t>
         </is>
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Costume off, make-up removal &amp; change</t>
+          <t>Wrap — pack, meet people, load-out</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr"/>
@@ -6291,38 +6291,20 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>9.20pm</t>
+          <t>9.50pm</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Wrap — pack, meet people, load-out</t>
+          <t>10.50pm</t>
+        </is>
+      </c>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Dinner near Jagriti Theatre (late return)</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>9.50pm</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>10.50pm</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>Dinner near Jagriti Theatre (late return)</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6484,7 +6466,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6494,19 +6476,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>37 min · 30 km · live traffic · 10 min loading first</t>
+          <t>39 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6519,12 +6501,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.37pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6537,12 +6519,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.37pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.52pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6555,7 +6537,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.52pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6732,7 +6714,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -6742,19 +6724,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>37 min · 30 km · live traffic · 10 min loading first</t>
+          <t>39 min · 26 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.17pm</t>
+          <t>5.19pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6767,12 +6749,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>5.37pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6785,12 +6767,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>5.37pm</t>
+          <t>5.39pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.52pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -6803,7 +6785,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.52pm</t>
+          <t>5.54pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>7.11am</t>
+          <t>7.14am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2236,19 +2236,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>33 min · 25 km · live traffic · 10 min loading first</t>
+          <t>34 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2261,12 +2261,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2279,12 +2279,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2297,7 +2297,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -2654,19 +2654,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>33 min · 25 km · live traffic · 10 min loading first</t>
+          <t>34 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.13am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -2679,12 +2679,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.23am</t>
+          <t>9.24am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2697,12 +2697,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.33am</t>
+          <t>9.34am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -2715,7 +2715,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.48am</t>
+          <t>9.49am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>3.48pm</t>
+          <t>3.47pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>33 min · 21 km · live traffic · 10 min loading first</t>
+          <t>32 min · 21 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.48pm</t>
+          <t>3.47pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.18pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3104,12 +3104,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.18pm</t>
+          <t>4.17pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>4.48pm</t>
+          <t>4.47pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3122,12 +3122,12 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>4.48pm</t>
+          <t>4.47pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>5.48pm</t>
+          <t>5.47pm</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -3140,7 +3140,7 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>5.48pm</t>
+          <t>5.47pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>1.54pm</t>
+          <t>1.53pm</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>34 min · 24 km · live traffic</t>
+          <t>33 min · 24 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>1.54pm</t>
+          <t>1.53pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
@@ -3916,12 +3916,12 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.54pm</t>
+          <t>1.53pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.54pm</t>
+          <t>2.53pm</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 26 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 29 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>7.11am</t>
+          <t>7.14am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4222,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 26 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 29 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>7.11am</t>
+          <t>7.14am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.41am</t>
+          <t>8.44am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.41am</t>
+          <t>8.44am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.11am</t>
+          <t>9.14am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.41am</t>
+          <t>9.44am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>6 h 45 · 387 km · live traffic · home about 5.32am (+1)</t>
+          <t>6 h 47 · 386 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4873,19 +4873,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 05 · 48 km · live traffic · 10 min loading first</t>
+          <t>1 h 02 · 50 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.27pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>7.00pm</t>
+          <t>6.57pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>9.14pm</t>
+          <t>9.13pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5265,14 +5265,14 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>1 h · 48 km · live traffic</t>
+          <t>59 min · 48 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.14pm</t>
+          <t>9.13pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.24am</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5482,19 +5482,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>33 min · 25 km · live traffic · 10 min loading first</t>
+          <t>34 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>6.23am</t>
+          <t>6.24am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.34am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5507,12 +5507,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>6.33am</t>
+          <t>6.34am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.49am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5525,7 +5525,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>6.48am</t>
+          <t>6.49am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5976,19 +5976,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>38 min · 24 km · live traffic · 10 min loading first</t>
+          <t>37 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>8.18am</t>
+          <t>8.17am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.28am</t>
+          <t>8.27am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -6001,12 +6001,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.28am</t>
+          <t>8.27am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.38am</t>
+          <t>8.37am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6019,12 +6019,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.38am</t>
+          <t>8.37am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>8.52am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6037,7 +6037,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.53am</t>
+          <t>8.52am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.31pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6150,19 +6150,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>43 min · 26 km · live traffic</t>
+          <t>41 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.33pm</t>
+          <t>1.31pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6175,12 +6175,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.03pm</t>
+          <t>2.01pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6193,7 +6193,7 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.33pm</t>
+          <t>2.31pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>7.14am</t>
+          <t>7.07am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4.45pm</t>
+          <t>4.46pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1394,19 +1394,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>40 min · 27 km · live traffic · 10 min loading first</t>
+          <t>41 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>4.45pm</t>
+          <t>4.46pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>4.55pm</t>
+          <t>4.56pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>4.55pm</t>
+          <t>4.56pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>3.47pm</t>
+          <t>3.48pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -3079,19 +3079,19 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>32 min · 21 km · live traffic · 10 min loading first</t>
+          <t>33 min · 21 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.47pm</t>
+          <t>3.48pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.18pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3104,12 +3104,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.17pm</t>
+          <t>4.18pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>4.47pm</t>
+          <t>4.48pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3122,12 +3122,12 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>4.47pm</t>
+          <t>4.48pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>5.47pm</t>
+          <t>5.48pm</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -3140,7 +3140,7 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>5.47pm</t>
+          <t>5.48pm</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -3328,19 +3328,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>35 min · 24 km · live traffic · 10 min loading first</t>
+          <t>36 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3353,12 +3353,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3371,12 +3371,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -3389,7 +3389,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -3739,19 +3739,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>35 min · 24 km · live traffic · 10 min loading first</t>
+          <t>36 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>9.15am</t>
+          <t>9.16am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -3764,12 +3764,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>9.25am</t>
+          <t>9.26am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -3782,12 +3782,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.35am</t>
+          <t>9.36am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -3800,7 +3800,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.50am</t>
+          <t>9.51am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>1.53pm</t>
+          <t>1.54pm</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>33 min · 24 km · live traffic</t>
+          <t>34 min · 24 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>1.53pm</t>
+          <t>1.54pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
@@ -3916,12 +3916,12 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.53pm</t>
+          <t>1.54pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.53pm</t>
+          <t>2.54pm</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 29 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 22 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>7.14am</t>
+          <t>7.07am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4222,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 29 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 22 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>7.14am</t>
+          <t>7.07am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.44am</t>
+          <t>8.37am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.44am</t>
+          <t>8.37am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.14am</t>
+          <t>9.07am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.37am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.44am</t>
+          <t>9.37am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>6 h 47 · 386 km · live traffic · home about 5.32am (+1)</t>
+          <t>6 h 52 · 387 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>1.56pm</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
@@ -4614,19 +4614,19 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>40 min · 27 km · live traffic · 10 min loading first</t>
+          <t>41 min · 27 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>1.56pm</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>2.25pm</t>
+          <t>2.26pm</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -4639,12 +4639,12 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>2.25pm</t>
+          <t>2.26pm</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>2.55pm</t>
+          <t>2.56pm</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -4657,12 +4657,12 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>2.55pm</t>
+          <t>2.56pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>3.55pm</t>
+          <t>3.56pm</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -4675,7 +4675,7 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>3.55pm</t>
+          <t>3.56pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
@@ -4863,7 +4863,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4873,19 +4873,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 02 · 50 km · live traffic · 10 min loading first</t>
+          <t>1 h 03 · 48 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.27pm</t>
+          <t>5.28pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.57pm</t>
+          <t>6.58pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>3.12pm</t>
+          <t>3.11pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5735,19 +5735,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>27 min · 18 km · live traffic · 10 min loading first</t>
+          <t>26 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>3.12pm</t>
+          <t>3.11pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.41pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5760,12 +5760,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.42pm</t>
+          <t>3.41pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.12pm</t>
+          <t>4.11pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5778,12 +5778,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.12pm</t>
+          <t>4.11pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.12pm</t>
+          <t>5.11pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5796,7 +5796,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.12pm</t>
+          <t>5.11pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -5966,7 +5966,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
@@ -5976,19 +5976,19 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>37 min · 24 km · live traffic · 10 min loading first</t>
+          <t>38 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>8.17am</t>
+          <t>8.18am</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>8.27am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -6001,12 +6001,12 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>8.27am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.37am</t>
+          <t>8.38am</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -6019,12 +6019,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.37am</t>
+          <t>8.38am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.52am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -6037,7 +6037,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.52am</t>
+          <t>8.53am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>7.07am</t>
+          <t>6.58am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>36 min · 25 km · live traffic · 10 min loading first</t>
+          <t>36 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>36 min · 25 km · live traffic · 10 min loading first</t>
+          <t>36 min · 24 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>1.54pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>34 min · 24 km · live traffic</t>
+          <t>35 min · 24 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>1.54pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
@@ -3916,12 +3916,12 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.54pm</t>
+          <t>1.55pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.54pm</t>
+          <t>2.55pm</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 22 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 13 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>7.07am</t>
+          <t>6.58am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4222,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 22 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 13 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>7.07am</t>
+          <t>6.58am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.37am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.37am</t>
+          <t>8.28am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>8.58am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>9.07am</t>
+          <t>8.58am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.37am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.37am</t>
+          <t>9.28am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>6 h 52 · 387 km · live traffic · home about 5.32am (+1)</t>
+          <t>6 h 56 · 387 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4873,19 +4873,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 03 · 48 km · live traffic · 10 min loading first</t>
+          <t>1 h 05 · 48 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.28pm</t>
+          <t>5.30pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>6.58pm</t>
+          <t>7.00pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>9.13pm</t>
+          <t>9.15pm</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
@@ -5265,14 +5265,14 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>59 min · 48 km · live traffic</t>
+          <t>1 h 01 · 48 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>9.13pm</t>
+          <t>9.15pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>3.11pm</t>
+          <t>3.12pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -5735,19 +5735,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>26 min · 18 km · live traffic · 10 min loading first</t>
+          <t>27 min · 18 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>3.11pm</t>
+          <t>3.12pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>3.41pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -5760,12 +5760,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>3.41pm</t>
+          <t>3.42pm</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>4.11pm</t>
+          <t>4.12pm</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -5778,12 +5778,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>4.11pm</t>
+          <t>4.12pm</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>5.11pm</t>
+          <t>5.12pm</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -5796,7 +5796,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>5.11pm</t>
+          <t>5.12pm</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.32pm</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -6150,19 +6150,19 @@
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>41 min · 29 km · live traffic</t>
+          <t>42 min · 29 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.31pm</t>
+          <t>1.32pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>2.02pm</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -6175,12 +6175,12 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>2.01pm</t>
+          <t>2.02pm</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.32pm</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -6193,7 +6193,7 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>2.31pm</t>
+          <t>2.32pm</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">

--- a/plan/tour-plan-20th-mile-routine.xlsx
+++ b/plan/tour-plan-20th-mile-routine.xlsx
@@ -1191,7 +1191,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>6.58am</t>
+          <t>6.59am</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>36 min · 24 km · live traffic · 10 min loading first</t>
+          <t>36 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>36 min · 24 km · live traffic · 10 min loading first</t>
+          <t>36 min · 25 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3881,7 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>1.54pm</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
@@ -3891,14 +3891,14 @@
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>35 min · 24 km · live traffic</t>
+          <t>34 min · 24 km · live traffic</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>1.54pm</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
@@ -3916,12 +3916,12 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>1.55pm</t>
+          <t>1.54pm</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>2.55pm</t>
+          <t>2.54pm</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -4133,7 +4133,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>7 h 13 · 414 km · live traffic · sleep on the road</t>
+          <t>7 h 14 · 414 km · live traffic · sleep on the road</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4211,7 @@
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>6.58am</t>
+          <t>6.59am</t>
         </is>
       </c>
       <c r="B7" s="11" t="inlineStr"/>
@@ -4222,19 +4222,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>7 h 13 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
+          <t>7 h 14 · 414 km · live traffic · left Yuvapatha 11.45pm on Thu, 15 Oct</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>6.58am</t>
+          <t>6.59am</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>8.28am</t>
+          <t>8.29am</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>8.28am</t>
+          <t>8.29am</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>8.58am</t>
+          <t>8.59am</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -4265,12 +4265,12 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>8.58am</t>
+          <t>8.59am</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>9.28am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -4283,7 +4283,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>9.28am</t>
+          <t>9.29am</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>6 h 56 · 387 km · live traffic · home about 5.32am (+1)</t>
+          <t>6 h 50 · 386 km · live traffic · home about 5.32am (+1)</t>
         </is>
       </c>
     </row>
@@ -4863,7 +4863,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4873,19 +4873,19 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>1 h 05 · 48 km · live traffic · 10 min loading first</t>
+          <t>1 h 04 · 48 km · live traffic · 10 min loading first</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>5.30pm</t>
+          <t>5.29pm</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>7.00pm</t>
+          <t>6.59pm</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
